--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1144,7 +1144,7 @@
       <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>ActionType</t>
+          <t>ActionBehavior</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="E4" s="0" t="inlineStr"/>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>行动类型：决定执行行动时走哪条结算分支</t>
+          <t>行动行为：决定执行行动时走哪条结算分支/由哪个 handler 执行</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr"/>
@@ -1178,11 +1178,11 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr"/>
-      <c r="B5" s="0" t="inlineStr"/>
-      <c r="C5" s="0" t="inlineStr"/>
-      <c r="D5" s="0" t="inlineStr"/>
+      <c r="B5" s="0" t="n"/>
+      <c r="C5" s="0" t="n"/>
+      <c r="D5" s="0" t="n"/>
       <c r="E5" s="0" t="inlineStr"/>
-      <c r="F5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="n"/>
       <c r="G5" s="0" t="inlineStr"/>
       <c r="H5" s="0" t="inlineStr">
         <is>
@@ -1198,11 +1198,11 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr"/>
-      <c r="B6" s="0" t="inlineStr"/>
-      <c r="C6" s="0" t="inlineStr"/>
-      <c r="D6" s="0" t="inlineStr"/>
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="n"/>
+      <c r="D6" s="0" t="n"/>
       <c r="E6" s="0" t="inlineStr"/>
-      <c r="F6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="n"/>
       <c r="G6" s="0" t="inlineStr"/>
       <c r="H6" s="0" t="inlineStr">
         <is>
@@ -1218,11 +1218,11 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr"/>
-      <c r="B7" s="0" t="inlineStr"/>
-      <c r="C7" s="0" t="inlineStr"/>
-      <c r="D7" s="0" t="inlineStr"/>
+      <c r="B7" s="0" t="n"/>
+      <c r="C7" s="0" t="n"/>
+      <c r="D7" s="0" t="n"/>
       <c r="E7" s="0" t="inlineStr"/>
-      <c r="F7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="n"/>
       <c r="G7" s="0" t="inlineStr"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
@@ -1238,11 +1238,11 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr"/>
-      <c r="B8" s="0" t="inlineStr"/>
-      <c r="C8" s="0" t="inlineStr"/>
-      <c r="D8" s="0" t="inlineStr"/>
+      <c r="B8" s="0" t="n"/>
+      <c r="C8" s="0" t="n"/>
+      <c r="D8" s="0" t="n"/>
       <c r="E8" s="0" t="inlineStr"/>
-      <c r="F8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="n"/>
       <c r="G8" s="0" t="inlineStr"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
@@ -1258,99 +1258,208 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr"/>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>TimelineNodeType</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="B9" s="0" t="n"/>
+      <c r="C9" s="0" t="n"/>
+      <c r="D9" s="0" t="n"/>
       <c r="E9" s="0" t="inlineStr"/>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>行动轴节点类型：推进天数经过整天位置时按序触发</t>
-        </is>
-      </c>
+      <c r="F9" s="0" t="n"/>
       <c r="G9" s="0" t="inlineStr"/>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9" s="0" t="inlineStr"/>
       <c r="L9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr"/>
-      <c r="B10" s="0" t="inlineStr"/>
-      <c r="C10" s="0" t="inlineStr"/>
-      <c r="D10" s="0" t="inlineStr"/>
-      <c r="E10" s="0" t="inlineStr"/>
-      <c r="F10" s="0" t="inlineStr"/>
-      <c r="G10" s="0" t="inlineStr"/>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr"/>
-      <c r="J10" s="0" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EffectType</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>局外即时效果类型：事件/奖励选项结果按它分派结算</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>无效果/占位</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="0" t="inlineStr"/>
-      <c r="L10" s="0" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr"/>
-      <c r="B11" s="0" t="inlineStr"/>
-      <c r="C11" s="0" t="inlineStr"/>
-      <c r="D11" s="0" t="inlineStr"/>
-      <c r="E11" s="0" t="inlineStr"/>
-      <c r="F11" s="0" t="inlineStr"/>
-      <c r="G11" s="0" t="inlineStr"/>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>获得金币(可负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LowerReq</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>降低本周目标分</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>获得道具(param=Active/Passive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>豪赌:成功翻倍失败扣除</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AddDish</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>菜谱加菜(占位折金币)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UpgradeDish</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>提升菜品(占位折金币)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>FoodBattle</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>跟进:进入美食战斗(value=目标分,param=modifier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr"/>
-      <c r="J11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr"/>
-      <c r="L11" s="0" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr"/>
-      <c r="B12" s="0" t="inlineStr"/>
-      <c r="C12" s="0" t="inlineStr"/>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr"/>
-      <c r="G12" s="0" t="inlineStr"/>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr"/>
-      <c r="J12" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="0" t="inlineStr"/>
-      <c r="L12" s="0" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>跟进:打开商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>GameOver</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>跟进:直接失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>跟进:直接通关</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1277,187 +1277,252 @@
       <c r="L9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>EffectType</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>局外即时效果类型：事件/奖励选项结果按它分派结算</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>无效果/占位</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>GainGold</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>获得金币(可负)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>LowerReq</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>降低本周目标分</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>GainItem</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>获得道具(param=Active/Passive)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Gamble</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>豪赌:成功翻倍失败扣除</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>AddDish</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>菜谱加菜(占位折金币)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>UpgradeDish</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>提升菜品(占位折金币)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>FoodBattle</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>跟进:进入美食战斗(value=目标分,param=modifier)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>跟进:打开商店</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>GameOver</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>跟进:直接失败</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>Victory</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>跟进:直接通关</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>FoodActionKind</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>美食行动类型：区分普通、超级与盛宴 Boss</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>普通美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>超级美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>Feast</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>盛宴(Boss)</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1462,65 +1462,320 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>FoodActionKind</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>美食行动类型：区分普通、超级与盛宴 Boss</t>
-        </is>
-      </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>AddHiddenScoreOffset</t>
         </is>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>普通美食行动</t>
+          <t>调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>EnqueueDishChoice</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>超级美食行动</t>
+          <t>入队菜品多选一奖励(value=候选数,param=标题)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
+          <t>EnqueueItemChoice</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>入队道具多选一奖励(value=候选数,param=Active/Passive|标题)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>AddRandomRecipeFlavor</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>给菜谱随机菜品添加随机风味(value=次数,优先无额外风味)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>GainSpecificItem</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>从指定道具列表随机获得道具(value=次数,param=id|id)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>GrantFragmentPack</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>获得餐桌碎片包(value=候选数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>AddShopPricePct</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>商店价格百分比修正(value=0.25 表示+25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>AddChoiceCountPenalty</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>后续奖励候选数惩罚(value=次数,param=数量变化,如-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>AddNextFoodTargetOffset</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>下一场美食目标分隐藏分偏移(value=偏移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>AddNextMealGold</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>下一次美食奖励额外金币(value=金币)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>RemoveActiveItemsForGold</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>失去所有主动道具并按件获得金币(value=每件金币)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>IncrementEventCounter</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t>增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>GainRandomFlavoredDishes</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>获得随机带风味菜品(value=数量)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>LoseAllGold</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>金币归零</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>GainLegendaryItem</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t>获得传奇被动道具，缺少传奇时回退高品质被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>UiTodo</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="K36" s="0" t="inlineStr">
+        <is>
+          <t>需要后续 UI 选目标的占位效果(param=提示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RemoveRandomRecipeDish</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>27</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>随机删除菜谱菜品(value=数量,param=flavored时只删带风味菜)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>FoodActionKind</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>美食行动类型：区分普通、超级与盛宴 Boss</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>普通美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>超级美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" s="0" t="inlineStr">
+        <is>
           <t>Feast</t>
         </is>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J40" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>盛宴(Boss)</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1702,80 +1702,95 @@
       </c>
     </row>
     <row r="37">
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>RemoveRandomRecipeDish</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>随机删除菜谱菜品(value=数量,param=flavored时只删带风味菜)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="0" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SelectRemoveRecipeDish</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>28</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>交互选择并删除菜谱中1道菜(事件专用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>FoodActionKind</t>
         </is>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D38" s="0" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F38" s="0" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>美食行动类型：区分普通、超级与盛宴 Boss</t>
         </is>
       </c>
-      <c r="H38" s="0" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="J38" s="0" t="n">
+      <c r="J39" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="0" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>普通美食行动</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="H39" s="0" t="inlineStr">
-        <is>
-          <t>Super</t>
-        </is>
-      </c>
-      <c r="J39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="0" t="inlineStr">
-        <is>
-          <t>超级美食行动</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>超级美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" s="0" t="inlineStr">
+        <is>
           <t>Feast</t>
         </is>
       </c>
-      <c r="J40" s="0" t="n">
+      <c r="J41" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K40" s="0" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>盛宴(Boss)</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1277,520 +1277,530 @@
       <c r="L9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="0" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>EffectType</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>局外即时效果类型：事件/奖励选项结果按它分派结算</t>
         </is>
       </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J11" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="0" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>无效果/占位</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>获得金币(可负)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>LowerReq</t>
+          <t>GainGold</t>
         </is>
       </c>
       <c r="J12" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>降低本周目标分</t>
+          <t>获得金币(可负)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>GainItem</t>
+          <t>LowerReq</t>
         </is>
       </c>
       <c r="J13" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>获得道具(param=Active/Passive)</t>
+          <t>降低本周目标分</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>Gamble</t>
+          <t>GainItem</t>
         </is>
       </c>
       <c r="J14" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>豪赌:成功翻倍失败扣除</t>
+          <t>获得道具(param=Active/Passive)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>AddDish</t>
+          <t>Gamble</t>
         </is>
       </c>
       <c r="J15" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>菜谱加菜(占位折金币)</t>
+          <t>豪赌:成功翻倍失败扣除</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>UpgradeDish</t>
+          <t>AddDish</t>
         </is>
       </c>
       <c r="J16" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>提升菜品(占位折金币)</t>
+          <t>菜谱加菜(占位折金币)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>FoodBattle</t>
+          <t>UpgradeDish</t>
         </is>
       </c>
       <c r="J17" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t>跟进:进入美食战斗(value=目标分,param=modifier)</t>
+          <t>提升菜品(占位折金币)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>FoodBattle</t>
         </is>
       </c>
       <c r="J18" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>跟进:打开商店</t>
+          <t>跟进:进入美食战斗(value=目标分,param=modifier)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>GameOver</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="J19" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>跟进:直接失败</t>
+          <t>跟进:打开商店</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>GameOver</t>
         </is>
       </c>
       <c r="J20" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>跟进:直接通关</t>
+          <t>跟进:直接失败</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>AddHiddenScoreOffset</t>
+          <t>Victory</t>
         </is>
       </c>
       <c r="J21" s="0" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</t>
+          <t>跟进:直接通关</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>EnqueueDishChoice</t>
+          <t>AddHiddenScoreOffset</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>入队菜品多选一奖励(value=候选数,param=标题)</t>
+          <t>调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>EnqueueItemChoice</t>
+          <t>EnqueueDishChoice</t>
         </is>
       </c>
       <c r="J23" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>入队道具多选一奖励(value=候选数,param=Active/Passive|标题)</t>
+          <t>入队菜品多选一奖励(value=候选数,param=标题)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>AddRandomRecipeFlavor</t>
+          <t>EnqueueItemChoice</t>
         </is>
       </c>
       <c r="J24" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>给菜谱随机菜品添加随机风味(value=次数,优先无额外风味)</t>
+          <t>入队道具多选一奖励(value=候选数,param=Active/Passive|标题)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>GainSpecificItem</t>
+          <t>AddRandomRecipeFlavor</t>
         </is>
       </c>
       <c r="J25" s="0" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>从指定道具列表随机获得道具(value=次数,param=id|id)</t>
+          <t>给菜谱随机菜品添加随机风味(value=次数,优先无额外风味)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>GrantFragmentPack</t>
+          <t>GainSpecificItem</t>
         </is>
       </c>
       <c r="J26" s="0" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>获得餐桌碎片包(value=候选数)</t>
+          <t>从指定道具列表随机获得道具(value=次数,param=id|id)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>AddShopPricePct</t>
+          <t>GrantFragmentPack</t>
         </is>
       </c>
       <c r="J27" s="0" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>商店价格百分比修正(value=0.25 表示+25%)</t>
+          <t>获得餐桌碎片包(value=候选数)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>AddChoiceCountPenalty</t>
+          <t>AddShopPricePct</t>
         </is>
       </c>
       <c r="J28" s="0" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>后续奖励候选数惩罚(value=次数,param=数量变化,如-1)</t>
+          <t>商店价格百分比修正(value=0.25 表示+25%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>AddNextFoodTargetOffset</t>
+          <t>AddChoiceCountPenalty</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>下一场美食目标分隐藏分偏移(value=偏移)</t>
+          <t>后续奖励候选数惩罚(value=次数,param=数量变化,如-1)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>AddNextMealGold</t>
+          <t>AddNextFoodTargetOffset</t>
         </is>
       </c>
       <c r="J30" s="0" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>下一次美食奖励额外金币(value=金币)</t>
+          <t>下一场美食目标分隐藏分偏移(value=偏移)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>RemoveActiveItemsForGold</t>
+          <t>AddNextMealGold</t>
         </is>
       </c>
       <c r="J31" s="0" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>失去所有主动道具并按件获得金币(value=每件金币)</t>
+          <t>下一次美食奖励额外金币(value=金币)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>IncrementEventCounter</t>
+          <t>RemoveActiveItemsForGold</t>
         </is>
       </c>
       <c r="J32" s="0" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</t>
+          <t>失去所有主动道具并按件获得金币(value=每件金币)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>GainRandomFlavoredDishes</t>
+          <t>IncrementEventCounter</t>
         </is>
       </c>
       <c r="J33" s="0" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>获得随机带风味菜品(value=数量)</t>
+          <t>增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>LoseAllGold</t>
+          <t>GainRandomFlavoredDishes</t>
         </is>
       </c>
       <c r="J34" s="0" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>金币归零</t>
+          <t>获得随机带风味菜品(value=数量)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>GainLegendaryItem</t>
+          <t>LoseAllGold</t>
         </is>
       </c>
       <c r="J35" s="0" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>获得传奇被动道具，缺少传奇时回退高品质被动</t>
+          <t>金币归零</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>UiTodo</t>
+          <t>GainLegendaryItem</t>
         </is>
       </c>
       <c r="J36" s="0" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>需要后续 UI 选目标的占位效果(param=提示)</t>
+          <t>获得传奇被动道具，缺少传奇时回退高品质被动</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
+          <t>UiTodo</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>需要后续 UI 选目标的占位效果(param=提示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
           <t>RemoveRandomRecipeDish</t>
         </is>
       </c>
-      <c r="J37" s="0" t="n">
+      <c r="J38" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="K37" s="0" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>随机删除菜谱菜品(value=数量,param=flavored时只删带风味菜)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="H38" t="inlineStr">
+    <row r="39">
+      <c r="H39" t="inlineStr">
         <is>
           <t>SelectRemoveRecipeDish</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>28</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>交互选择并删除菜谱中1道菜(事件专用)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="0" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>FoodActionKind</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>美食行动类型：区分普通、超级与盛宴 Boss</t>
         </is>
       </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="J39" s="0" t="n">
+      <c r="J40" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>普通美食行动</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>Super</t>
-        </is>
-      </c>
-      <c r="J40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="0" t="inlineStr">
-        <is>
-          <t>超级美食行动</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>超级美食行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
           <t>Feast</t>
         </is>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J42" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="0" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>盛宴(Boss)</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd4571fe3024426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60ff5894ff6448fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1260,459 +1260,712 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="B11" t="inlineStr">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11" t="str">
+        <x:v>Slot</x:v>
+      </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>独立抽奖机行动</x:v>
+      </x:c>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">EffectType</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" t="inlineStr">
+      <x:c r="C12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" t="inlineStr">
+      <x:c r="D12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" t="inlineStr">
+      <x:c r="E12"/>
+      <x:c r="F12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">局外即时效果类型：事件/奖励选项结果按它分派结算</x:t>
         </x:is>
       </x:c>
-      <x:c r="H11" t="inlineStr">
+      <x:c r="G12"/>
+      <x:c r="H12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11" t="n">
+      <x:c r="I12"/>
+      <x:c r="J12" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" t="inlineStr">
+      <x:c r="K12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">无效果/占位</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="H12" t="inlineStr">
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
         </x:is>
       </x:c>
-      <x:c r="J12" t="n">
+      <x:c r="I13"/>
+      <x:c r="J13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" t="inlineStr">
+      <x:c r="K13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">获得金币(可负)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="H13" t="inlineStr">
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LowerReq</x:t>
         </x:is>
       </x:c>
-      <x:c r="J13" t="n">
+      <x:c r="I14"/>
+      <x:c r="J14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K13" t="inlineStr">
+      <x:c r="K14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">降低本周目标分</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="H14" t="inlineStr">
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainItem</x:t>
         </x:is>
       </x:c>
-      <x:c r="J14" t="n">
+      <x:c r="I15"/>
+      <x:c r="J15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K14" t="inlineStr">
+      <x:c r="K15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">获得道具(param=Active/Passive)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="H15" t="inlineStr">
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Gamble</x:t>
         </x:is>
       </x:c>
-      <x:c r="J15" t="n">
+      <x:c r="I16"/>
+      <x:c r="J16" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K15" t="inlineStr">
+      <x:c r="K16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">豪赌:成功翻倍失败扣除</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="H16" t="inlineStr">
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" t="n">
+      <x:c r="I17"/>
+      <x:c r="J17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K16" t="inlineStr">
+      <x:c r="K17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">菜谱加菜(占位折金币)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="H17" t="inlineStr">
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UpgradeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="J17" t="n">
+      <x:c r="I18"/>
+      <x:c r="J18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K17" t="inlineStr">
+      <x:c r="K18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">提升菜品(占位折金币)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="H18" t="inlineStr">
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">FoodBattle</x:t>
         </x:is>
       </x:c>
-      <x:c r="J18" t="n">
+      <x:c r="I19"/>
+      <x:c r="J19" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K18" t="inlineStr">
+      <x:c r="K19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跟进:进入美食战斗(value=目标分,param=modifier)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="H19" t="inlineStr">
+      <x:c r="L19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Shop</x:t>
         </x:is>
       </x:c>
-      <x:c r="J19" t="n">
+      <x:c r="I20"/>
+      <x:c r="J20" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K19" t="inlineStr">
+      <x:c r="K20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跟进:打开商店</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="H20" t="inlineStr">
+      <x:c r="L20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GameOver</x:t>
         </x:is>
       </x:c>
-      <x:c r="J20" t="n">
+      <x:c r="I21"/>
+      <x:c r="J21" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K20" t="inlineStr">
+      <x:c r="K21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跟进:直接失败</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="H21" t="inlineStr">
+      <x:c r="L21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Victory</x:t>
         </x:is>
       </x:c>
-      <x:c r="J21" t="n">
+      <x:c r="I22"/>
+      <x:c r="J22" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K21" t="inlineStr">
+      <x:c r="K22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跟进:直接通关</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="H22" t="inlineStr">
+      <x:c r="L22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
         </x:is>
       </x:c>
-      <x:c r="J22" t="n">
+      <x:c r="I23"/>
+      <x:c r="J23" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K22" t="inlineStr">
+      <x:c r="K23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="H23" t="inlineStr">
+      <x:c r="L23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">EnqueueDishChoice</x:t>
         </x:is>
       </x:c>
-      <x:c r="J23" t="n">
+      <x:c r="I24"/>
+      <x:c r="J24" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K23" t="inlineStr">
+      <x:c r="K24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">入队菜品多选一奖励(value=候选数,param=标题)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="H24" t="inlineStr">
+      <x:c r="L24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">EnqueueItemChoice</x:t>
         </x:is>
       </x:c>
-      <x:c r="J24" t="n">
+      <x:c r="I25"/>
+      <x:c r="J25" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K24" t="inlineStr">
+      <x:c r="K25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">入队道具多选一奖励(value=候选数,param=Active/Passive|标题)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="H25" t="inlineStr">
+      <x:c r="L25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddRandomRecipeFlavor</x:t>
         </x:is>
       </x:c>
-      <x:c r="J25" t="n">
+      <x:c r="I26"/>
+      <x:c r="J26" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K25" t="inlineStr">
+      <x:c r="K26" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">给菜谱随机菜品添加随机风味(value=次数,优先无额外风味)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="H26" t="inlineStr">
+      <x:c r="L26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainSpecificItem</x:t>
         </x:is>
       </x:c>
-      <x:c r="J26" t="n">
+      <x:c r="I27"/>
+      <x:c r="J27" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K26" t="inlineStr">
+      <x:c r="K27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">从指定道具列表随机获得道具(value=次数,param=id|id)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="H27" t="inlineStr">
+      <x:c r="L27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantFragmentPack</x:t>
         </x:is>
       </x:c>
-      <x:c r="J27" t="n">
+      <x:c r="I28"/>
+      <x:c r="J28" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K27" t="inlineStr">
+      <x:c r="K28" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">获得餐桌碎片包(value=候选数)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="H28" t="inlineStr">
+      <x:c r="L28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddShopPricePct</x:t>
         </x:is>
       </x:c>
-      <x:c r="J28" t="n">
+      <x:c r="I29"/>
+      <x:c r="J29" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K28" t="inlineStr">
+      <x:c r="K29" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">商店价格百分比修正(value=0.25 表示+25%)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="H29" t="inlineStr">
+      <x:c r="L29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddChoiceCountPenalty</x:t>
         </x:is>
       </x:c>
-      <x:c r="J29" t="n">
+      <x:c r="I30"/>
+      <x:c r="J30" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K29" t="inlineStr">
+      <x:c r="K30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">后续奖励候选数惩罚(value=次数,param=数量变化,如-1)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="H30" t="inlineStr">
+      <x:c r="L30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddNextFoodTargetOffset</x:t>
         </x:is>
       </x:c>
-      <x:c r="J30" t="n">
+      <x:c r="I31"/>
+      <x:c r="J31" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K30" t="inlineStr">
+      <x:c r="K31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">下一场美食目标分隐藏分偏移(value=偏移)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="H31" t="inlineStr">
+      <x:c r="L31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddNextMealGold</x:t>
         </x:is>
       </x:c>
-      <x:c r="J31" t="n">
+      <x:c r="I32"/>
+      <x:c r="J32" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K31" t="inlineStr">
+      <x:c r="K32" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">下一次美食奖励额外金币(value=金币)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="H32" t="inlineStr">
+      <x:c r="L32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RemoveActiveItemsForGold</x:t>
         </x:is>
       </x:c>
-      <x:c r="J32" t="n">
+      <x:c r="I33"/>
+      <x:c r="J33" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K32" t="inlineStr">
+      <x:c r="K33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">失去所有主动道具并按件获得金币(value=每件金币)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="H33" t="inlineStr">
+      <x:c r="L33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">IncrementEventCounter</x:t>
         </x:is>
       </x:c>
-      <x:c r="J33" t="n">
+      <x:c r="I34"/>
+      <x:c r="J34" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K33" t="inlineStr">
+      <x:c r="K34" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="H34" t="inlineStr">
+      <x:c r="L34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J34" t="n">
+      <x:c r="I35"/>
+      <x:c r="J35" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K34" t="inlineStr">
+      <x:c r="K35" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">获得随机带风味菜品(value=数量)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="H35" t="inlineStr">
+      <x:c r="L35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseAllGold</x:t>
         </x:is>
       </x:c>
-      <x:c r="J35" t="n">
+      <x:c r="I36"/>
+      <x:c r="J36" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K35" t="inlineStr">
+      <x:c r="K36" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">金币归零</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="H36" t="inlineStr">
+      <x:c r="L36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainLegendaryItem</x:t>
         </x:is>
       </x:c>
-      <x:c r="J36" t="n">
+      <x:c r="I37"/>
+      <x:c r="J37" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K36" t="inlineStr">
+      <x:c r="K37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">获得传奇被动道具，缺少传奇时回退高品质被动</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="H37" t="inlineStr">
+      <x:c r="L37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UiTodo</x:t>
         </x:is>
       </x:c>
-      <x:c r="J37" t="n">
+      <x:c r="I38"/>
+      <x:c r="J38" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K37" t="inlineStr">
+      <x:c r="K38" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">需要后续 UI 选目标的占位效果(param=提示)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="H38" t="inlineStr">
+      <x:c r="L38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RemoveRandomRecipeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="J38" t="n">
+      <x:c r="I39"/>
+      <x:c r="J39" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K38" t="inlineStr">
+      <x:c r="K39" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">随机删除菜谱菜品(value=数量,param=flavored时只删带风味菜)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="H39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SelectRemoveRecipeDish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J39" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="K39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">交互选择并删除菜谱中1道菜(事件专用)</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40"/>
@@ -1722,78 +1975,78 @@
       <x:c r="E40"/>
       <x:c r="F40"/>
       <x:c r="G40"/>
-      <x:c r="H40" t="str">
-        <x:v>CollectInterest</x:v>
+      <x:c r="H40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SelectRemoveRecipeDish</x:t>
+        </x:is>
       </x:c>
       <x:c r="I40"/>
       <x:c r="J40" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K40" t="str">
-        <x:v>按当前金币及运行时利息参数结算；param=事件ID，读取event.resultText模板</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">交互选择并删除菜谱中1道菜(事件专用)</x:t>
+        </x:is>
       </x:c>
       <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41"/>
-      <x:c r="B41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FoodActionKind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
       <x:c r="E41"/>
-      <x:c r="F41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">美食行动类型：区分普通、超级与盛宴 Boss</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="F41"/>
       <x:c r="G41"/>
-      <x:c r="H41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Normal</x:t>
-        </x:is>
+      <x:c r="H41" t="str">
+        <x:v>CollectInterest</x:v>
       </x:c>
       <x:c r="I41"/>
       <x:c r="J41" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">普通美食行动</x:t>
-        </x:is>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>按当前金币及运行时利息参数结算；param=事件ID，读取event.resultText模板</x:v>
       </x:c>
       <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
-      <x:c r="B42"/>
-      <x:c r="C42"/>
-      <x:c r="D42"/>
+      <x:c r="B42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FoodActionKind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">False</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">False</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E42"/>
-      <x:c r="F42"/>
+      <x:c r="F42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">美食行动类型：区分普通、超级与盛宴 Boss</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G42"/>
       <x:c r="H42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Super</x:t>
+          <x:t xml:space="preserve">Normal</x:t>
         </x:is>
       </x:c>
       <x:c r="I42"/>
       <x:c r="J42" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">超级美食行动</x:t>
+          <x:t xml:space="preserve">普通美食行动</x:t>
         </x:is>
       </x:c>
       <x:c r="L42"/>
@@ -1808,19 +2061,43 @@
       <x:c r="G43"/>
       <x:c r="H43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Feast</x:t>
+          <x:t xml:space="preserve">Super</x:t>
         </x:is>
       </x:c>
       <x:c r="I43"/>
       <x:c r="J43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K43" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">超级美食行动</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44"/>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Feast</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I44"/>
+      <x:c r="J44" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K43" t="inlineStr">
+      <x:c r="K44" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">盛宴(Boss)</x:t>
         </x:is>
       </x:c>
-      <x:c r="L43"/>
+      <x:c r="L44"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60ff5894ff6448fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43175225152c42d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1672,10 +1672,8 @@
       <x:c r="J27" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从指定道具列表随机获得道具(value=次数,param=id|id)</x:t>
-        </x:is>
+      <x:c r="K27" t="str">
+        <x:v>按奖励槽组生成道具奖励(param=奖励槽组ID)</x:v>
       </x:c>
       <x:c r="L27"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43175225152c42d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R786126af26214168"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1360,10 +1360,8 @@
       <x:c r="J14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">降低本周目标分</x:t>
-        </x:is>
+      <x:c r="K14" t="str">
+        <x:v>降低本周目标美味值</x:v>
       </x:c>
       <x:c r="L14"/>
     </x:row>
@@ -1384,10 +1382,8 @@
       <x:c r="J15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得道具(param=Active/Passive)</x:t>
-        </x:is>
+      <x:c r="K15" t="str">
+        <x:v>获得装饰品或消耗品(param=Active/Passive)</x:v>
       </x:c>
       <x:c r="L15"/>
     </x:row>
@@ -1432,10 +1428,8 @@
       <x:c r="J17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜谱加菜(占位折金币)</x:t>
-        </x:is>
+      <x:c r="K17" t="str">
+        <x:v>食谱加菜(占位折金币)</x:v>
       </x:c>
       <x:c r="L17"/>
     </x:row>
@@ -1456,10 +1450,8 @@
       <x:c r="J18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">提升菜品(占位折金币)</x:t>
-        </x:is>
+      <x:c r="K18" t="str">
+        <x:v>提升食物(占位折金币)</x:v>
       </x:c>
       <x:c r="L18"/>
     </x:row>
@@ -1480,10 +1472,8 @@
       <x:c r="J19" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟进:进入美食战斗(value=目标分,param=modifier)</x:t>
-        </x:is>
+      <x:c r="K19" t="str">
+        <x:v>跟进:进入经营挑战(value=目标美味值,param=modifier)</x:v>
       </x:c>
       <x:c r="L19"/>
     </x:row>
@@ -1600,10 +1590,8 @@
       <x:c r="J24" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">入队菜品多选一奖励(value=候选数,param=标题)</x:t>
-        </x:is>
+      <x:c r="K24" t="str">
+        <x:v>入队食物多选一奖励(value=候选数,param=标题)</x:v>
       </x:c>
       <x:c r="L24"/>
     </x:row>
@@ -1624,10 +1612,8 @@
       <x:c r="J25" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">入队道具多选一奖励(value=候选数,param=Active/Passive|标题)</x:t>
-        </x:is>
+      <x:c r="K25" t="str">
+        <x:v>入队装饰品或消耗品多选一奖励(value=候选数,param=Active/Passive|标题)</x:v>
       </x:c>
       <x:c r="L25"/>
     </x:row>
@@ -1648,10 +1634,8 @@
       <x:c r="J26" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">给菜谱随机菜品添加随机风味(value=次数,优先无额外风味)</x:t>
-        </x:is>
+      <x:c r="K26" t="str">
+        <x:v>给食谱随机食物添加随机风味(value=次数,优先无额外风味)</x:v>
       </x:c>
       <x:c r="L26"/>
     </x:row>
@@ -1673,7 +1657,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>按奖励槽组生成道具奖励(param=奖励槽组ID)</x:v>
+        <x:v>按奖励槽组生成装饰品或消耗品奖励(param=奖励槽组ID)</x:v>
       </x:c>
       <x:c r="L27"/>
     </x:row>
@@ -1694,10 +1678,8 @@
       <x:c r="J28" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得餐桌碎片包(value=候选数)</x:t>
-        </x:is>
+      <x:c r="K28" t="str">
+        <x:v>获得餐桌格包(value=候选数)</x:v>
       </x:c>
       <x:c r="L28"/>
     </x:row>
@@ -1718,10 +1700,8 @@
       <x:c r="J29" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">商店价格百分比修正(value=0.25 表示+25%)</x:t>
-        </x:is>
+      <x:c r="K29" t="str">
+        <x:v>商店价格百分比修正(value=0.25 表示 +25%)</x:v>
       </x:c>
       <x:c r="L29"/>
     </x:row>
@@ -1742,10 +1722,8 @@
       <x:c r="J30" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">后续奖励候选数惩罚(value=次数,param=数量变化,如-1)</x:t>
-        </x:is>
+      <x:c r="K30" t="str">
+        <x:v>后续奖励候选数惩罚(value=次数,param=数量变化,如 -1)</x:v>
       </x:c>
       <x:c r="L30"/>
     </x:row>
@@ -1766,10 +1744,8 @@
       <x:c r="J31" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下一场美食目标分隐藏分偏移(value=偏移)</x:t>
-        </x:is>
+      <x:c r="K31" t="str">
+        <x:v>下一场经营挑战目标美味值隐藏分偏移(value=偏移)</x:v>
       </x:c>
       <x:c r="L31"/>
     </x:row>
@@ -1790,10 +1766,8 @@
       <x:c r="J32" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下一次美食奖励额外金币(value=金币)</x:t>
-        </x:is>
+      <x:c r="K32" t="str">
+        <x:v>下一场经营挑战奖励额外金币(value=金币)</x:v>
       </x:c>
       <x:c r="L32"/>
     </x:row>
@@ -1814,10 +1788,8 @@
       <x:c r="J33" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">失去所有主动道具并按件获得金币(value=每件金币)</x:t>
-        </x:is>
+      <x:c r="K33" t="str">
+        <x:v>失去所有消耗品并按件获得金币(value=每件金币)</x:v>
       </x:c>
       <x:c r="L33"/>
     </x:row>
@@ -1862,10 +1834,8 @@
       <x:c r="J35" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得随机带风味菜品(value=数量)</x:t>
-        </x:is>
+      <x:c r="K35" t="str">
+        <x:v>获得随机带风味食物(value=数量)</x:v>
       </x:c>
       <x:c r="L35"/>
     </x:row>
@@ -1910,10 +1880,8 @@
       <x:c r="J37" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得传奇被动道具，缺少传奇时回退高品质被动</x:t>
-        </x:is>
+      <x:c r="K37" t="str">
+        <x:v>获得传奇装饰品，缺少传奇时回退高品质被动</x:v>
       </x:c>
       <x:c r="L37"/>
     </x:row>
@@ -1958,10 +1926,8 @@
       <x:c r="J39" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">随机删除菜谱菜品(value=数量,param=flavored时只删带风味菜)</x:t>
-        </x:is>
+      <x:c r="K39" t="str">
+        <x:v>随机删除食谱食物(value=数量,param=flavored时只删带风味菜)</x:v>
       </x:c>
       <x:c r="L39"/>
     </x:row>
@@ -1982,10 +1948,8 @@
       <x:c r="J40" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">交互选择并删除菜谱中1道菜(事件专用)</x:t>
-        </x:is>
+      <x:c r="K40" t="str">
+        <x:v>交互选择并删除食谱中1 个食物(事件专用)</x:v>
       </x:c>
       <x:c r="L40"/>
     </x:row>
@@ -2027,10 +1991,8 @@
         </x:is>
       </x:c>
       <x:c r="E42"/>
-      <x:c r="F42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">美食行动类型：区分普通、超级与盛宴 Boss</x:t>
-        </x:is>
+      <x:c r="F42" t="str">
+        <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
       </x:c>
       <x:c r="G42"/>
       <x:c r="H42" t="inlineStr">
@@ -2042,10 +2004,8 @@
       <x:c r="J42" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">普通美食行动</x:t>
-        </x:is>
+      <x:c r="K42" t="str">
+        <x:v>日常营业行动</x:v>
       </x:c>
       <x:c r="L42"/>
     </x:row>
@@ -2066,10 +2026,8 @@
       <x:c r="J43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">超级美食行动</x:t>
-        </x:is>
+      <x:c r="K43" t="str">
+        <x:v>火热营业行动</x:v>
       </x:c>
       <x:c r="L43"/>
     </x:row>
@@ -2090,10 +2048,8 @@
       <x:c r="J44" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盛宴(Boss)</x:t>
-        </x:is>
+      <x:c r="K44" t="str">
+        <x:v>星级评鉴</x:v>
       </x:c>
       <x:c r="L44"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -1975,37 +1975,25 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
-      <x:c r="B42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FoodActionKind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
       <x:c r="E42"/>
-      <x:c r="F42" t="str">
-        <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
-      </x:c>
+      <x:c r="F42"/>
       <x:c r="G42"/>
       <x:c r="H42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Normal</x:t>
+          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
         </x:is>
       </x:c>
       <x:c r="I42"/>
       <x:c r="J42" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K42" t="str">
-        <x:v>日常营业行动</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">营业基础金币百分比修正(value=百分比,param=Next/CurrentWeek)</x:t>
+        </x:is>
       </x:c>
       <x:c r="L42"/>
     </x:row>
@@ -2019,15 +2007,17 @@
       <x:c r="G43"/>
       <x:c r="H43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Super</x:t>
+          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
         </x:is>
       </x:c>
       <x:c r="I43"/>
       <x:c r="J43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K43" t="str">
-        <x:v>火热营业行动</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K43" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数增加(value=分数)</x:t>
+        </x:is>
       </x:c>
       <x:c r="L43"/>
     </x:row>
@@ -2041,17 +2031,171 @@
       <x:c r="G44"/>
       <x:c r="H44" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Feast</x:t>
+          <x:t xml:space="preserve">AddBossTargetScorePct</x:t>
         </x:is>
       </x:c>
       <x:c r="I44"/>
       <x:c r="J44" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">后续星级评鉴目标美味值永久百分比修正(value=百分比)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AddBossBaseGoldPct</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I45"/>
+      <x:c r="J45" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K45" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">后续星级评鉴基础金币永久百分比修正(value=百分比)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46"/>
+      <x:c r="B46"/>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">随机消耗品(value=数量,param=指定ID列表或Adjust；支持放回)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">随机装饰品(value=数量,param=Positive/Negative)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FoodActionKind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">False</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">False</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48"/>
+      <x:c r="F48" t="str">
+        <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
+      </x:c>
+      <x:c r="G48"/>
+      <x:c r="H48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Normal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I48"/>
+      <x:c r="J48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>日常营业行动</x:v>
+      </x:c>
+      <x:c r="L48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+      <x:c r="G49"/>
+      <x:c r="H49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Super</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I49"/>
+      <x:c r="J49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>火热营业行动</x:v>
+      </x:c>
+      <x:c r="L49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+      <x:c r="G50"/>
+      <x:c r="H50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Feast</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I50"/>
+      <x:c r="J50" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K44" t="str">
+      <x:c r="K50" t="str">
         <x:v>星级评鉴</x:v>
       </x:c>
-      <x:c r="L44"/>
+      <x:c r="L50"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R786126af26214168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43df3943362143e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,410 +854,224 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">full_name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">unique</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">group</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">*items</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>full_name</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>flags</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>unique</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>comment</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="str">
+        <x:v>*items</x:v>
+      </x:c>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">alias</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
+      <x:c r="A2" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>alias</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>value</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>comment</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>tags</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">全名(包含模块和名字)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">枚举项是否唯一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">枚举名</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">别名</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">值</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">注释</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A3" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>全名(包含模块和名字)</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>枚举项是否唯一</x:v>
+      </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3" t="str">
+        <x:v>枚举名</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>别名</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>值</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>注释</x:v>
+      </x:c>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActionBehavior</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行动行为：决定执行行动时走哪条结算分支/由哪个 handler 执行</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Event</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A4"/>
+      <x:c r="B4" t="str">
+        <x:v>ActionBehavior</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4" t="str">
+        <x:v>行动行为：决定执行行动时走哪条结算分支/由哪个 handler 执行</x:v>
+      </x:c>
+      <x:c r="G4"/>
+      <x:c r="H4" t="str">
+        <x:v>Event</x:v>
+      </x:c>
+      <x:c r="I4"/>
       <x:c r="J4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="n"/>
-      <x:c r="C5" t="n"/>
-      <x:c r="D5" t="n"/>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="n"/>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Food</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="I5"/>
       <x:c r="J5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="n"/>
-      <x:c r="C6" t="n"/>
-      <x:c r="D6" t="n"/>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F6" t="n"/>
-      <x:c r="G6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reward</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6" t="str">
+        <x:v>Reward</x:v>
+      </x:c>
+      <x:c r="I6"/>
       <x:c r="J6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="n"/>
-      <x:c r="C7" t="n"/>
-      <x:c r="D7" t="n"/>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F7" t="n"/>
-      <x:c r="G7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Negative</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="I7"/>
       <x:c r="J7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="n"/>
-      <x:c r="C8" t="n"/>
-      <x:c r="D8" t="n"/>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F8" t="n"/>
-      <x:c r="G8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shop</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8" t="str">
+        <x:v>Shop</x:v>
+      </x:c>
+      <x:c r="I8"/>
       <x:c r="J8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B9" t="n"/>
-      <x:c r="C9" t="n"/>
-      <x:c r="D9" t="n"/>
-      <x:c r="E9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F9" t="n"/>
-      <x:c r="G9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9" t="str">
+        <x:v>Interest</x:v>
+      </x:c>
+      <x:c r="I9"/>
       <x:c r="J9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="L9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="H10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Effect</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J10">
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10" t="str">
+        <x:v>Effect</x:v>
+      </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -1281,41 +1095,29 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
-      <x:c r="B12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EffectType</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
+      <x:c r="B12" t="str">
+        <x:v>EffectType</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>False</x:v>
       </x:c>
       <x:c r="E12"/>
-      <x:c r="F12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">局外即时效果类型：事件/奖励选项结果按它分派结算</x:t>
-        </x:is>
+      <x:c r="F12" t="str">
+        <x:v>局外即时效果类型：事件/奖励选项结果按它分派结算</x:v>
       </x:c>
       <x:c r="G12"/>
-      <x:c r="H12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
+      <x:c r="H12" t="str">
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I12"/>
       <x:c r="J12" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无效果/占位</x:t>
-        </x:is>
+      <x:c r="K12" t="str">
+        <x:v>无效果/占位</x:v>
       </x:c>
       <x:c r="L12"/>
     </x:row>
@@ -1327,19 +1129,15 @@
       <x:c r="E13"/>
       <x:c r="F13"/>
       <x:c r="G13"/>
-      <x:c r="H13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainGold</x:t>
-        </x:is>
+      <x:c r="H13" t="str">
+        <x:v>GainGold</x:v>
       </x:c>
       <x:c r="I13"/>
       <x:c r="J13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得金币(可负)</x:t>
-        </x:is>
+      <x:c r="K13" t="str">
+        <x:v>获得金币(可负)</x:v>
       </x:c>
       <x:c r="L13"/>
     </x:row>
@@ -1351,10 +1149,8 @@
       <x:c r="E14"/>
       <x:c r="F14"/>
       <x:c r="G14"/>
-      <x:c r="H14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LowerReq</x:t>
-        </x:is>
+      <x:c r="H14" t="str">
+        <x:v>LowerReq</x:v>
       </x:c>
       <x:c r="I14"/>
       <x:c r="J14" t="n">
@@ -1373,10 +1169,8 @@
       <x:c r="E15"/>
       <x:c r="F15"/>
       <x:c r="G15"/>
-      <x:c r="H15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainItem</x:t>
-        </x:is>
+      <x:c r="H15" t="str">
+        <x:v>GainItem</x:v>
       </x:c>
       <x:c r="I15"/>
       <x:c r="J15" t="n">
@@ -1395,19 +1189,15 @@
       <x:c r="E16"/>
       <x:c r="F16"/>
       <x:c r="G16"/>
-      <x:c r="H16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gamble</x:t>
-        </x:is>
+      <x:c r="H16" t="str">
+        <x:v>Gamble</x:v>
       </x:c>
       <x:c r="I16"/>
       <x:c r="J16" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">豪赌:成功翻倍失败扣除</x:t>
-        </x:is>
+      <x:c r="K16" t="str">
+        <x:v>豪赌:成功翻倍失败扣除</x:v>
       </x:c>
       <x:c r="L16"/>
     </x:row>
@@ -1419,10 +1209,8 @@
       <x:c r="E17"/>
       <x:c r="F17"/>
       <x:c r="G17"/>
-      <x:c r="H17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddDish</x:t>
-        </x:is>
+      <x:c r="H17" t="str">
+        <x:v>AddDish</x:v>
       </x:c>
       <x:c r="I17"/>
       <x:c r="J17" t="n">
@@ -1441,10 +1229,8 @@
       <x:c r="E18"/>
       <x:c r="F18"/>
       <x:c r="G18"/>
-      <x:c r="H18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UpgradeDish</x:t>
-        </x:is>
+      <x:c r="H18" t="str">
+        <x:v>UpgradeDish</x:v>
       </x:c>
       <x:c r="I18"/>
       <x:c r="J18" t="n">
@@ -1463,10 +1249,8 @@
       <x:c r="E19"/>
       <x:c r="F19"/>
       <x:c r="G19"/>
-      <x:c r="H19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FoodBattle</x:t>
-        </x:is>
+      <x:c r="H19" t="str">
+        <x:v>FoodBattle</x:v>
       </x:c>
       <x:c r="I19"/>
       <x:c r="J19" t="n">
@@ -1485,19 +1269,15 @@
       <x:c r="E20"/>
       <x:c r="F20"/>
       <x:c r="G20"/>
-      <x:c r="H20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shop</x:t>
-        </x:is>
+      <x:c r="H20" t="str">
+        <x:v>Shop</x:v>
       </x:c>
       <x:c r="I20"/>
       <x:c r="J20" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟进:打开商店</x:t>
-        </x:is>
+      <x:c r="K20" t="str">
+        <x:v>跟进:打开商店</x:v>
       </x:c>
       <x:c r="L20"/>
     </x:row>
@@ -1509,19 +1289,15 @@
       <x:c r="E21"/>
       <x:c r="F21"/>
       <x:c r="G21"/>
-      <x:c r="H21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GameOver</x:t>
-        </x:is>
+      <x:c r="H21" t="str">
+        <x:v>GameOver</x:v>
       </x:c>
       <x:c r="I21"/>
       <x:c r="J21" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟进:直接失败</x:t>
-        </x:is>
+      <x:c r="K21" t="str">
+        <x:v>跟进:直接失败</x:v>
       </x:c>
       <x:c r="L21"/>
     </x:row>
@@ -1533,19 +1309,15 @@
       <x:c r="E22"/>
       <x:c r="F22"/>
       <x:c r="G22"/>
-      <x:c r="H22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Victory</x:t>
-        </x:is>
+      <x:c r="H22" t="str">
+        <x:v>Victory</x:v>
       </x:c>
       <x:c r="I22"/>
       <x:c r="J22" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟进:直接通关</x:t>
-        </x:is>
+      <x:c r="K22" t="str">
+        <x:v>跟进:直接通关</x:v>
       </x:c>
       <x:c r="L22"/>
     </x:row>
@@ -1557,19 +1329,15 @@
       <x:c r="E23"/>
       <x:c r="F23"/>
       <x:c r="G23"/>
-      <x:c r="H23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
-        </x:is>
+      <x:c r="H23" t="str">
+        <x:v>AddHiddenScoreOffset</x:v>
       </x:c>
       <x:c r="I23"/>
       <x:c r="J23" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</x:t>
-        </x:is>
+      <x:c r="K23" t="str">
+        <x:v>调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</x:v>
       </x:c>
       <x:c r="L23"/>
     </x:row>
@@ -1581,10 +1349,8 @@
       <x:c r="E24"/>
       <x:c r="F24"/>
       <x:c r="G24"/>
-      <x:c r="H24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnqueueDishChoice</x:t>
-        </x:is>
+      <x:c r="H24" t="str">
+        <x:v>EnqueueDishChoice</x:v>
       </x:c>
       <x:c r="I24"/>
       <x:c r="J24" t="n">
@@ -1603,10 +1369,8 @@
       <x:c r="E25"/>
       <x:c r="F25"/>
       <x:c r="G25"/>
-      <x:c r="H25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnqueueItemChoice</x:t>
-        </x:is>
+      <x:c r="H25" t="str">
+        <x:v>EnqueueItemChoice</x:v>
       </x:c>
       <x:c r="I25"/>
       <x:c r="J25" t="n">
@@ -1625,10 +1389,8 @@
       <x:c r="E26"/>
       <x:c r="F26"/>
       <x:c r="G26"/>
-      <x:c r="H26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddRandomRecipeFlavor</x:t>
-        </x:is>
+      <x:c r="H26" t="str">
+        <x:v>AddRandomRecipeFlavor</x:v>
       </x:c>
       <x:c r="I26"/>
       <x:c r="J26" t="n">
@@ -1647,10 +1409,8 @@
       <x:c r="E27"/>
       <x:c r="F27"/>
       <x:c r="G27"/>
-      <x:c r="H27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainSpecificItem</x:t>
-        </x:is>
+      <x:c r="H27" t="str">
+        <x:v>GainSpecificItem</x:v>
       </x:c>
       <x:c r="I27"/>
       <x:c r="J27" t="n">
@@ -1669,10 +1429,8 @@
       <x:c r="E28"/>
       <x:c r="F28"/>
       <x:c r="G28"/>
-      <x:c r="H28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GrantFragmentPack</x:t>
-        </x:is>
+      <x:c r="H28" t="str">
+        <x:v>GrantFragmentPack</x:v>
       </x:c>
       <x:c r="I28"/>
       <x:c r="J28" t="n">
@@ -1691,10 +1449,8 @@
       <x:c r="E29"/>
       <x:c r="F29"/>
       <x:c r="G29"/>
-      <x:c r="H29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddShopPricePct</x:t>
-        </x:is>
+      <x:c r="H29" t="str">
+        <x:v>AddShopPricePct</x:v>
       </x:c>
       <x:c r="I29"/>
       <x:c r="J29" t="n">
@@ -1713,10 +1469,8 @@
       <x:c r="E30"/>
       <x:c r="F30"/>
       <x:c r="G30"/>
-      <x:c r="H30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddChoiceCountPenalty</x:t>
-        </x:is>
+      <x:c r="H30" t="str">
+        <x:v>AddChoiceCountPenalty</x:v>
       </x:c>
       <x:c r="I30"/>
       <x:c r="J30" t="n">
@@ -1735,10 +1489,8 @@
       <x:c r="E31"/>
       <x:c r="F31"/>
       <x:c r="G31"/>
-      <x:c r="H31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddNextFoodTargetOffset</x:t>
-        </x:is>
+      <x:c r="H31" t="str">
+        <x:v>AddNextFoodTargetOffset</x:v>
       </x:c>
       <x:c r="I31"/>
       <x:c r="J31" t="n">
@@ -1757,10 +1509,8 @@
       <x:c r="E32"/>
       <x:c r="F32"/>
       <x:c r="G32"/>
-      <x:c r="H32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddNextMealGold</x:t>
-        </x:is>
+      <x:c r="H32" t="str">
+        <x:v>AddNextMealGold</x:v>
       </x:c>
       <x:c r="I32"/>
       <x:c r="J32" t="n">
@@ -1779,10 +1529,8 @@
       <x:c r="E33"/>
       <x:c r="F33"/>
       <x:c r="G33"/>
-      <x:c r="H33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RemoveActiveItemsForGold</x:t>
-        </x:is>
+      <x:c r="H33" t="str">
+        <x:v>RemoveActiveItemsForGold</x:v>
       </x:c>
       <x:c r="I33"/>
       <x:c r="J33" t="n">
@@ -1801,19 +1549,15 @@
       <x:c r="E34"/>
       <x:c r="F34"/>
       <x:c r="G34"/>
-      <x:c r="H34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">IncrementEventCounter</x:t>
-        </x:is>
+      <x:c r="H34" t="str">
+        <x:v>IncrementEventCounter</x:v>
       </x:c>
       <x:c r="I34"/>
       <x:c r="J34" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</x:t>
-        </x:is>
+      <x:c r="K34" t="str">
+        <x:v>增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</x:v>
       </x:c>
       <x:c r="L34"/>
     </x:row>
@@ -1825,10 +1569,8 @@
       <x:c r="E35"/>
       <x:c r="F35"/>
       <x:c r="G35"/>
-      <x:c r="H35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
-        </x:is>
+      <x:c r="H35" t="str">
+        <x:v>GainRandomFlavoredDishes</x:v>
       </x:c>
       <x:c r="I35"/>
       <x:c r="J35" t="n">
@@ -1847,19 +1589,15 @@
       <x:c r="E36"/>
       <x:c r="F36"/>
       <x:c r="G36"/>
-      <x:c r="H36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LoseAllGold</x:t>
-        </x:is>
+      <x:c r="H36" t="str">
+        <x:v>LoseAllGold</x:v>
       </x:c>
       <x:c r="I36"/>
       <x:c r="J36" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金币归零</x:t>
-        </x:is>
+      <x:c r="K36" t="str">
+        <x:v>金币归零</x:v>
       </x:c>
       <x:c r="L36"/>
     </x:row>
@@ -1871,10 +1609,8 @@
       <x:c r="E37"/>
       <x:c r="F37"/>
       <x:c r="G37"/>
-      <x:c r="H37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainLegendaryItem</x:t>
-        </x:is>
+      <x:c r="H37" t="str">
+        <x:v>GainLegendaryItem</x:v>
       </x:c>
       <x:c r="I37"/>
       <x:c r="J37" t="n">
@@ -1893,19 +1629,15 @@
       <x:c r="E38"/>
       <x:c r="F38"/>
       <x:c r="G38"/>
-      <x:c r="H38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UiTodo</x:t>
-        </x:is>
+      <x:c r="H38" t="str">
+        <x:v>UiTodo</x:v>
       </x:c>
       <x:c r="I38"/>
       <x:c r="J38" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">需要后续 UI 选目标的占位效果(param=提示)</x:t>
-        </x:is>
+      <x:c r="K38" t="str">
+        <x:v>需要后续 UI 选目标的占位效果(param=提示)</x:v>
       </x:c>
       <x:c r="L38"/>
     </x:row>
@@ -1917,10 +1649,8 @@
       <x:c r="E39"/>
       <x:c r="F39"/>
       <x:c r="G39"/>
-      <x:c r="H39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RemoveRandomRecipeDish</x:t>
-        </x:is>
+      <x:c r="H39" t="str">
+        <x:v>RemoveRandomRecipeDish</x:v>
       </x:c>
       <x:c r="I39"/>
       <x:c r="J39" t="n">
@@ -1939,10 +1669,8 @@
       <x:c r="E40"/>
       <x:c r="F40"/>
       <x:c r="G40"/>
-      <x:c r="H40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SelectRemoveRecipeDish</x:t>
-        </x:is>
+      <x:c r="H40" t="str">
+        <x:v>SelectRemoveRecipeDish</x:v>
       </x:c>
       <x:c r="I40"/>
       <x:c r="J40" t="n">
@@ -1981,19 +1709,15 @@
       <x:c r="E42"/>
       <x:c r="F42"/>
       <x:c r="G42"/>
-      <x:c r="H42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
-        </x:is>
+      <x:c r="H42" t="str">
+        <x:v>AddBusinessGoldPct</x:v>
       </x:c>
       <x:c r="I42"/>
       <x:c r="J42" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">营业基础金币百分比修正(value=百分比,param=Next/CurrentWeek)</x:t>
-        </x:is>
+      <x:c r="K42" t="str">
+        <x:v>营业基础金币百分比修正(value=百分比,param=Next/CurrentWeek)</x:v>
       </x:c>
       <x:c r="L42"/>
     </x:row>
@@ -2005,19 +1729,15 @@
       <x:c r="E43"/>
       <x:c r="F43"/>
       <x:c r="G43"/>
-      <x:c r="H43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
-        </x:is>
+      <x:c r="H43" t="str">
+        <x:v>AddAllRecipeScoreFlat</x:v>
       </x:c>
       <x:c r="I43"/>
       <x:c r="J43" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数增加(value=分数)</x:t>
-        </x:is>
+      <x:c r="K43" t="str">
+        <x:v>触发时食谱中已有的全部食物永久分数增加(value=分数)</x:v>
       </x:c>
       <x:c r="L43"/>
     </x:row>
@@ -2029,19 +1749,15 @@
       <x:c r="E44"/>
       <x:c r="F44"/>
       <x:c r="G44"/>
-      <x:c r="H44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddBossTargetScorePct</x:t>
-        </x:is>
+      <x:c r="H44" t="str">
+        <x:v>AddBossTargetScorePct</x:v>
       </x:c>
       <x:c r="I44"/>
       <x:c r="J44" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">后续星级评鉴目标美味值永久百分比修正(value=百分比)</x:t>
-        </x:is>
+      <x:c r="K44" t="str">
+        <x:v>后续星级评鉴目标美味值永久百分比修正(value=百分比)</x:v>
       </x:c>
       <x:c r="L44"/>
     </x:row>
@@ -2053,19 +1769,15 @@
       <x:c r="E45"/>
       <x:c r="F45"/>
       <x:c r="G45"/>
-      <x:c r="H45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddBossBaseGoldPct</x:t>
-        </x:is>
+      <x:c r="H45" t="str">
+        <x:v>AddBossBaseGoldPct</x:v>
       </x:c>
       <x:c r="I45"/>
       <x:c r="J45" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">后续星级评鉴基础金币永久百分比修正(value=百分比)</x:t>
-        </x:is>
+      <x:c r="K45" t="str">
+        <x:v>后续星级评鉴基础金币永久百分比修正(value=百分比)</x:v>
       </x:c>
       <x:c r="L45"/>
     </x:row>
@@ -2077,19 +1789,15 @@
       <x:c r="E46"/>
       <x:c r="F46"/>
       <x:c r="G46"/>
-      <x:c r="H46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
-        </x:is>
+      <x:c r="H46" t="str">
+        <x:v>GrantRandomActiveItems</x:v>
       </x:c>
       <x:c r="I46"/>
       <x:c r="J46" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">随机消耗品(value=数量,param=指定ID列表或Adjust；支持放回)</x:t>
-        </x:is>
+      <x:c r="K46" t="str">
+        <x:v>随机消耗品(value=数量,param=指定ID列表或Adjust；支持放回)</x:v>
       </x:c>
       <x:c r="L46"/>
     </x:row>
@@ -2101,77 +1809,63 @@
       <x:c r="E47"/>
       <x:c r="F47"/>
       <x:c r="G47"/>
-      <x:c r="H47" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
-        </x:is>
+      <x:c r="H47" t="str">
+        <x:v>GrantRandomPassiveItems</x:v>
       </x:c>
       <x:c r="I47"/>
       <x:c r="J47" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K47" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">随机装饰品(value=数量,param=Positive/Negative)</x:t>
-        </x:is>
+      <x:c r="K47" t="str">
+        <x:v>随机装饰品(value=数量,param=Positive/Negative)</x:v>
       </x:c>
       <x:c r="L47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48"/>
-      <x:c r="B48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FoodActionKind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">False</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
       <x:c r="E48"/>
-      <x:c r="F48" t="str">
-        <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
-      </x:c>
+      <x:c r="F48"/>
       <x:c r="G48"/>
-      <x:c r="H48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Normal</x:t>
-        </x:is>
+      <x:c r="H48" t="str">
+        <x:v>LoseEscalatingGold</x:v>
       </x:c>
       <x:c r="I48"/>
       <x:c r="J48" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>日常营业行动</x:v>
+        <x:v>递增扣除金币(value=首次金额,param=counterId|每次增量；不足扣到0)</x:v>
       </x:c>
       <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49"/>
-      <x:c r="B49"/>
-      <x:c r="C49"/>
-      <x:c r="D49"/>
+      <x:c r="B49" t="str">
+        <x:v>FoodActionKind</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E49"/>
-      <x:c r="F49"/>
+      <x:c r="F49" t="str">
+        <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
+      </x:c>
       <x:c r="G49"/>
-      <x:c r="H49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Super</x:t>
-        </x:is>
+      <x:c r="H49" t="str">
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="I49"/>
       <x:c r="J49" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>火热营业行动</x:v>
+        <x:v>日常营业行动</x:v>
       </x:c>
       <x:c r="L49"/>
     </x:row>
@@ -2183,19 +1877,37 @@
       <x:c r="E50"/>
       <x:c r="F50"/>
       <x:c r="G50"/>
-      <x:c r="H50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feast</x:t>
-        </x:is>
+      <x:c r="H50" t="str">
+        <x:v>Super</x:v>
       </x:c>
       <x:c r="I50"/>
       <x:c r="J50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>火热营业行动</x:v>
+      </x:c>
+      <x:c r="L50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51" t="str">
+        <x:v>Feast</x:v>
+      </x:c>
+      <x:c r="I51"/>
+      <x:c r="J51" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K50" t="str">
+      <x:c r="K51" t="str">
         <x:v>星级评鉴</x:v>
       </x:c>
-      <x:c r="L50"/>
+      <x:c r="L51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/GourmetProject/GameConfig/Datas/__enums_action.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_action.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43df3943362143e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re62a729c7ef64047"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="20">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -123,8 +123,19 @@
       <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="宋体"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="宋体"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -286,8 +297,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F3F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="18">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -368,6 +384,96 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -518,7 +624,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -526,6 +632,84 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -844,1070 +1028,1144 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="8.247618675231934" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="32" style="2" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" style="2" hidden="0" customWidth="1"/>
     <x:col min="4" max="5" width="10" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.380952835083008" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="7.5714287757873535" style="2" customWidth="1"/>
-    <x:col min="8" max="8" width="13.504761695861816" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="12.628571510314941" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="68" style="2" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" style="2" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="35" style="2" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" style="2" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="66" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>flags</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>unique</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E1" s="13" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F1" s="13" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="13" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="str">
+      <x:c r="H1" s="13" t="str">
         <x:v>*items</x:v>
       </x:c>
-      <x:c r="I1"/>
-      <x:c r="J1"/>
-      <x:c r="K1"/>
-      <x:c r="L1"/>
+      <x:c r="I1" s="13"/>
+      <x:c r="J1" s="13"/>
+      <x:c r="K1" s="13"/>
+      <x:c r="L1" s="22"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
+      <x:c r="A2" s="23" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2"/>
-      <x:c r="C2"/>
-      <x:c r="D2"/>
-      <x:c r="E2"/>
-      <x:c r="F2"/>
-      <x:c r="G2"/>
-      <x:c r="H2" t="str">
+      <x:c r="B2" s="24"/>
+      <x:c r="C2" s="24"/>
+      <x:c r="D2" s="24"/>
+      <x:c r="E2" s="24"/>
+      <x:c r="F2" s="24"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="24" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I2" s="24" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="J2" s="24" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K2" s="24" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="L2" t="str">
+      <x:c r="L2" s="25" t="str">
         <x:v>tags</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="A3" s="26" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B3" s="27" t="str">
         <x:v>全名(包含模块和名字)</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C3" s="27" t="str">
         <x:v>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D3" s="27" t="str">
         <x:v>枚举项是否唯一</x:v>
       </x:c>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
-      <x:c r="G3"/>
-      <x:c r="H3" t="str">
+      <x:c r="E3" s="27"/>
+      <x:c r="F3" s="27"/>
+      <x:c r="G3" s="27"/>
+      <x:c r="H3" s="27" t="str">
         <x:v>枚举名</x:v>
       </x:c>
-      <x:c r="I3" t="str">
+      <x:c r="I3" s="27" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="J3" s="27" t="str">
         <x:v>值</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K3" s="27" t="str">
         <x:v>注释</x:v>
       </x:c>
-      <x:c r="L3"/>
+      <x:c r="L3" s="28"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4"/>
-      <x:c r="B4" t="str">
+      <x:c r="A4" s="5"/>
+      <x:c r="B4" s="5" t="str">
         <x:v>ActionBehavior</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="E4"/>
-      <x:c r="F4" t="str">
+      <x:c r="E4" s="5"/>
+      <x:c r="F4" s="5" t="str">
         <x:v>行动行为：决定执行行动时走哪条结算分支/由哪个 handler 执行</x:v>
       </x:c>
-      <x:c r="G4"/>
-      <x:c r="H4" t="str">
+      <x:c r="G4" s="5"/>
+      <x:c r="H4" s="5" t="str">
         <x:v>Event</x:v>
       </x:c>
-      <x:c r="I4"/>
-      <x:c r="J4" t="n">
+      <x:c r="I4" s="5"/>
+      <x:c r="J4" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K4"/>
-      <x:c r="L4"/>
+      <x:c r="K4" s="5"/>
+      <x:c r="L4" s="5"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5"/>
-      <x:c r="B5"/>
-      <x:c r="C5"/>
-      <x:c r="D5"/>
-      <x:c r="E5"/>
-      <x:c r="F5"/>
-      <x:c r="G5"/>
-      <x:c r="H5" t="str">
+      <x:c r="A5" s="5"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="5"/>
+      <x:c r="D5" s="5"/>
+      <x:c r="E5" s="5"/>
+      <x:c r="F5" s="5"/>
+      <x:c r="G5" s="5"/>
+      <x:c r="H5" s="5" t="str">
         <x:v>Food</x:v>
       </x:c>
-      <x:c r="I5"/>
-      <x:c r="J5" t="n">
+      <x:c r="I5" s="5"/>
+      <x:c r="J5" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5"/>
-      <x:c r="L5"/>
+      <x:c r="K5" s="5"/>
+      <x:c r="L5" s="5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6"/>
-      <x:c r="B6"/>
-      <x:c r="C6"/>
-      <x:c r="D6"/>
-      <x:c r="E6"/>
-      <x:c r="F6"/>
-      <x:c r="G6"/>
-      <x:c r="H6" t="str">
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="5"/>
+      <x:c r="G6" s="5"/>
+      <x:c r="H6" s="5" t="str">
         <x:v>Reward</x:v>
       </x:c>
-      <x:c r="I6"/>
-      <x:c r="J6" t="n">
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6"/>
-      <x:c r="L6"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
-      <x:c r="H7" t="str">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="5"/>
+      <x:c r="D7" s="5"/>
+      <x:c r="E7" s="5"/>
+      <x:c r="F7" s="5"/>
+      <x:c r="G7" s="5"/>
+      <x:c r="H7" s="5" t="str">
         <x:v>Negative</x:v>
       </x:c>
-      <x:c r="I7"/>
-      <x:c r="J7" t="n">
+      <x:c r="I7" s="5"/>
+      <x:c r="J7" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7"/>
-      <x:c r="L7"/>
+      <x:c r="K7" s="5"/>
+      <x:c r="L7" s="5"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8" t="str">
+      <x:c r="A8" s="5"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="5"/>
+      <x:c r="D8" s="5"/>
+      <x:c r="E8" s="5"/>
+      <x:c r="F8" s="5"/>
+      <x:c r="G8" s="5"/>
+      <x:c r="H8" s="5" t="str">
         <x:v>Shop</x:v>
       </x:c>
-      <x:c r="I8"/>
-      <x:c r="J8" t="n">
+      <x:c r="I8" s="5"/>
+      <x:c r="J8" s="5" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K8"/>
-      <x:c r="L8"/>
+      <x:c r="K8" s="5"/>
+      <x:c r="L8" s="5"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9" t="str">
+      <x:c r="A9" s="5"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="5"/>
+      <x:c r="D9" s="5"/>
+      <x:c r="E9" s="5"/>
+      <x:c r="F9" s="5"/>
+      <x:c r="G9" s="5"/>
+      <x:c r="H9" s="5" t="str">
         <x:v>Interest</x:v>
       </x:c>
-      <x:c r="I9"/>
-      <x:c r="J9" t="n">
+      <x:c r="I9" s="5"/>
+      <x:c r="J9" s="5" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K9"/>
-      <x:c r="L9"/>
+      <x:c r="K9" s="5"/>
+      <x:c r="L9" s="5"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10"/>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-      <x:c r="H10" t="str">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="5"/>
+      <x:c r="D10" s="5"/>
+      <x:c r="E10" s="5"/>
+      <x:c r="F10" s="5"/>
+      <x:c r="G10" s="5"/>
+      <x:c r="H10" s="5" t="str">
         <x:v>Effect</x:v>
       </x:c>
-      <x:c r="I10"/>
-      <x:c r="J10" t="n">
+      <x:c r="I10" s="5"/>
+      <x:c r="J10" s="5" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K10"/>
-      <x:c r="L10"/>
+      <x:c r="K10" s="5"/>
+      <x:c r="L10" s="5"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11" t="str">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="5"/>
+      <x:c r="F11" s="5"/>
+      <x:c r="G11" s="5"/>
+      <x:c r="H11" s="5" t="str">
         <x:v>Slot</x:v>
       </x:c>
-      <x:c r="I11"/>
-      <x:c r="J11" t="n">
+      <x:c r="I11" s="5"/>
+      <x:c r="J11" s="5" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K11" s="5" t="str">
         <x:v>独立抽奖机行动</x:v>
       </x:c>
-      <x:c r="L11"/>
+      <x:c r="L11" s="5"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12" t="str">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5" t="str">
         <x:v>EffectType</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C12" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="D12" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="E12"/>
-      <x:c r="F12" t="str">
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="5" t="str">
         <x:v>局外即时效果类型：事件/奖励选项结果按它分派结算</x:v>
       </x:c>
-      <x:c r="G12"/>
-      <x:c r="H12" t="str">
+      <x:c r="G12" s="5"/>
+      <x:c r="H12" s="5" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I12"/>
-      <x:c r="J12" t="n">
+      <x:c r="I12" s="5"/>
+      <x:c r="J12" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" t="str">
+      <x:c r="K12" s="5" t="str">
         <x:v>无效果/占位</x:v>
       </x:c>
-      <x:c r="L12"/>
+      <x:c r="L12" s="5"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13" t="str">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="5"/>
+      <x:c r="G13" s="5"/>
+      <x:c r="H13" s="5" t="str">
         <x:v>GainGold</x:v>
       </x:c>
-      <x:c r="I13"/>
-      <x:c r="J13" t="n">
+      <x:c r="I13" s="5"/>
+      <x:c r="J13" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" t="str">
+      <x:c r="K13" s="5" t="str">
         <x:v>获得金币(可负)</x:v>
       </x:c>
-      <x:c r="L13"/>
+      <x:c r="L13" s="5"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14" t="str">
+      <x:c r="A14" s="5"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="5"/>
+      <x:c r="D14" s="5"/>
+      <x:c r="E14" s="5"/>
+      <x:c r="F14" s="5"/>
+      <x:c r="G14" s="5"/>
+      <x:c r="H14" s="5" t="str">
         <x:v>LowerReq</x:v>
       </x:c>
-      <x:c r="I14"/>
-      <x:c r="J14" t="n">
+      <x:c r="I14" s="5"/>
+      <x:c r="J14" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K14" t="str">
+      <x:c r="K14" s="5" t="str">
         <x:v>降低本周目标美味值</x:v>
       </x:c>
-      <x:c r="L14"/>
+      <x:c r="L14" s="5"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15" t="str">
+      <x:c r="A15" s="5"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="5"/>
+      <x:c r="D15" s="5"/>
+      <x:c r="E15" s="5"/>
+      <x:c r="F15" s="5"/>
+      <x:c r="G15" s="5"/>
+      <x:c r="H15" s="5" t="str">
         <x:v>GainItem</x:v>
       </x:c>
-      <x:c r="I15"/>
-      <x:c r="J15" t="n">
+      <x:c r="I15" s="5"/>
+      <x:c r="J15" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K15" t="str">
+      <x:c r="K15" s="5" t="str">
         <x:v>获得装饰品或消耗品(param=Active/Passive)</x:v>
       </x:c>
-      <x:c r="L15"/>
+      <x:c r="L15" s="5"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16" t="str">
+      <x:c r="A16" s="5"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="5"/>
+      <x:c r="D16" s="5"/>
+      <x:c r="E16" s="5"/>
+      <x:c r="F16" s="5"/>
+      <x:c r="G16" s="5"/>
+      <x:c r="H16" s="5" t="str">
         <x:v>Gamble</x:v>
       </x:c>
-      <x:c r="I16"/>
-      <x:c r="J16" t="n">
+      <x:c r="I16" s="5"/>
+      <x:c r="J16" s="5" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K16" t="str">
+      <x:c r="K16" s="5" t="str">
         <x:v>豪赌:成功翻倍失败扣除</x:v>
       </x:c>
-      <x:c r="L16"/>
+      <x:c r="L16" s="5"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17" t="str">
+      <x:c r="A17" s="5"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="5"/>
+      <x:c r="D17" s="5"/>
+      <x:c r="E17" s="5"/>
+      <x:c r="F17" s="5"/>
+      <x:c r="G17" s="5"/>
+      <x:c r="H17" s="5" t="str">
         <x:v>AddDish</x:v>
       </x:c>
-      <x:c r="I17"/>
-      <x:c r="J17" t="n">
+      <x:c r="I17" s="5"/>
+      <x:c r="J17" s="5" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K17" t="str">
+      <x:c r="K17" s="5" t="str">
         <x:v>食谱加菜(占位折金币)</x:v>
       </x:c>
-      <x:c r="L17"/>
+      <x:c r="L17" s="5"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18" t="str">
+      <x:c r="A18" s="5"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="5"/>
+      <x:c r="D18" s="5"/>
+      <x:c r="E18" s="5"/>
+      <x:c r="F18" s="5"/>
+      <x:c r="G18" s="5"/>
+      <x:c r="H18" s="5" t="str">
         <x:v>UpgradeDish</x:v>
       </x:c>
-      <x:c r="I18"/>
-      <x:c r="J18" t="n">
+      <x:c r="I18" s="5"/>
+      <x:c r="J18" s="5" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K18" t="str">
+      <x:c r="K18" s="5" t="str">
         <x:v>提升食物(占位折金币)</x:v>
       </x:c>
-      <x:c r="L18"/>
+      <x:c r="L18" s="5"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19" t="str">
+      <x:c r="A19" s="5"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="5"/>
+      <x:c r="D19" s="5"/>
+      <x:c r="E19" s="5"/>
+      <x:c r="F19" s="5"/>
+      <x:c r="G19" s="5"/>
+      <x:c r="H19" s="5" t="str">
         <x:v>FoodBattle</x:v>
       </x:c>
-      <x:c r="I19"/>
-      <x:c r="J19" t="n">
+      <x:c r="I19" s="5"/>
+      <x:c r="J19" s="5" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K19" t="str">
+      <x:c r="K19" s="5" t="str">
         <x:v>跟进:进入经营挑战(value=目标美味值,param=modifier)</x:v>
       </x:c>
-      <x:c r="L19"/>
+      <x:c r="L19" s="5"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20" t="str">
+      <x:c r="A20" s="5"/>
+      <x:c r="B20" s="5"/>
+      <x:c r="C20" s="5"/>
+      <x:c r="D20" s="5"/>
+      <x:c r="E20" s="5"/>
+      <x:c r="F20" s="5"/>
+      <x:c r="G20" s="5"/>
+      <x:c r="H20" s="5" t="str">
         <x:v>Shop</x:v>
       </x:c>
-      <x:c r="I20"/>
-      <x:c r="J20" t="n">
+      <x:c r="I20" s="5"/>
+      <x:c r="J20" s="5" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K20" t="str">
+      <x:c r="K20" s="5" t="str">
         <x:v>跟进:打开商店</x:v>
       </x:c>
-      <x:c r="L20"/>
+      <x:c r="L20" s="5"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21" t="str">
+      <x:c r="A21" s="5"/>
+      <x:c r="B21" s="5"/>
+      <x:c r="C21" s="5"/>
+      <x:c r="D21" s="5"/>
+      <x:c r="E21" s="5"/>
+      <x:c r="F21" s="5"/>
+      <x:c r="G21" s="5"/>
+      <x:c r="H21" s="5" t="str">
         <x:v>GameOver</x:v>
       </x:c>
-      <x:c r="I21"/>
-      <x:c r="J21" t="n">
+      <x:c r="I21" s="5"/>
+      <x:c r="J21" s="5" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K21" t="str">
+      <x:c r="K21" s="5" t="str">
         <x:v>跟进:直接失败</x:v>
       </x:c>
-      <x:c r="L21"/>
+      <x:c r="L21" s="5"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22" t="str">
+      <x:c r="A22" s="5"/>
+      <x:c r="B22" s="5"/>
+      <x:c r="C22" s="5"/>
+      <x:c r="D22" s="5"/>
+      <x:c r="E22" s="5"/>
+      <x:c r="F22" s="5"/>
+      <x:c r="G22" s="5"/>
+      <x:c r="H22" s="5" t="str">
         <x:v>Victory</x:v>
       </x:c>
-      <x:c r="I22"/>
-      <x:c r="J22" t="n">
+      <x:c r="I22" s="5"/>
+      <x:c r="J22" s="5" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K22" t="str">
+      <x:c r="K22" s="5" t="str">
         <x:v>跟进:直接通关</x:v>
       </x:c>
-      <x:c r="L22"/>
+      <x:c r="L22" s="5"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23" t="str">
+      <x:c r="A23" s="5"/>
+      <x:c r="B23" s="5"/>
+      <x:c r="C23" s="5"/>
+      <x:c r="D23" s="5"/>
+      <x:c r="E23" s="5"/>
+      <x:c r="F23" s="5"/>
+      <x:c r="G23" s="5"/>
+      <x:c r="H23" s="5" t="str">
         <x:v>AddHiddenScoreOffset</x:v>
       </x:c>
-      <x:c r="I23"/>
-      <x:c r="J23" t="n">
+      <x:c r="I23" s="5"/>
+      <x:c r="J23" s="5" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K23" t="str">
+      <x:c r="K23" s="5" t="str">
         <x:v>调整隐藏分偏移(param=TargetScore/Dish/PassiveItem/Fragment/Gold/Reward/All,value=偏移)</x:v>
       </x:c>
-      <x:c r="L23"/>
+      <x:c r="L23" s="5"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24" t="str">
+      <x:c r="A24" s="5"/>
+      <x:c r="B24" s="5"/>
+      <x:c r="C24" s="5"/>
+      <x:c r="D24" s="5"/>
+      <x:c r="E24" s="5"/>
+      <x:c r="F24" s="5"/>
+      <x:c r="G24" s="5"/>
+      <x:c r="H24" s="5" t="str">
         <x:v>EnqueueDishChoice</x:v>
       </x:c>
-      <x:c r="I24"/>
-      <x:c r="J24" t="n">
+      <x:c r="I24" s="5"/>
+      <x:c r="J24" s="5" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K24" t="str">
+      <x:c r="K24" s="5" t="str">
         <x:v>入队食物多选一奖励(value=候选数,param=标题)</x:v>
       </x:c>
-      <x:c r="L24"/>
+      <x:c r="L24" s="5"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25" t="str">
+      <x:c r="A25" s="5"/>
+      <x:c r="B25" s="5"/>
+      <x:c r="C25" s="5"/>
+      <x:c r="D25" s="5"/>
+      <x:c r="E25" s="5"/>
+      <x:c r="F25" s="5"/>
+      <x:c r="G25" s="5"/>
+      <x:c r="H25" s="5" t="str">
         <x:v>EnqueueItemChoice</x:v>
       </x:c>
-      <x:c r="I25"/>
-      <x:c r="J25" t="n">
+      <x:c r="I25" s="5"/>
+      <x:c r="J25" s="5" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K25" t="str">
+      <x:c r="K25" s="5" t="str">
         <x:v>入队装饰品或消耗品多选一奖励(value=候选数,param=Active/Passive|标题)</x:v>
       </x:c>
-      <x:c r="L25"/>
+      <x:c r="L25" s="5"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26" t="str">
+      <x:c r="A26" s="5"/>
+      <x:c r="B26" s="5"/>
+      <x:c r="C26" s="5"/>
+      <x:c r="D26" s="5"/>
+      <x:c r="E26" s="5"/>
+      <x:c r="F26" s="5"/>
+      <x:c r="G26" s="5"/>
+      <x:c r="H26" s="5" t="str">
         <x:v>AddRandomRecipeFlavor</x:v>
       </x:c>
-      <x:c r="I26"/>
-      <x:c r="J26" t="n">
+      <x:c r="I26" s="5"/>
+      <x:c r="J26" s="5" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K26" t="str">
+      <x:c r="K26" s="5" t="str">
         <x:v>给食谱随机食物添加随机风味(value=次数,优先无额外风味)</x:v>
       </x:c>
-      <x:c r="L26"/>
+      <x:c r="L26" s="5"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27" t="str">
+      <x:c r="A27" s="5"/>
+      <x:c r="B27" s="5"/>
+      <x:c r="C27" s="5"/>
+      <x:c r="D27" s="5"/>
+      <x:c r="E27" s="5"/>
+      <x:c r="F27" s="5"/>
+      <x:c r="G27" s="5"/>
+      <x:c r="H27" s="5" t="str">
         <x:v>GainSpecificItem</x:v>
       </x:c>
-      <x:c r="I27"/>
-      <x:c r="J27" t="n">
+      <x:c r="I27" s="5"/>
+      <x:c r="J27" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K27" t="str">
+      <x:c r="K27" s="5" t="str">
         <x:v>按奖励槽组生成装饰品或消耗品奖励(param=奖励槽组ID)</x:v>
       </x:c>
-      <x:c r="L27"/>
+      <x:c r="L27" s="5"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28" t="str">
+      <x:c r="A28" s="5"/>
+      <x:c r="B28" s="5"/>
+      <x:c r="C28" s="5"/>
+      <x:c r="D28" s="5"/>
+      <x:c r="E28" s="5"/>
+      <x:c r="F28" s="5"/>
+      <x:c r="G28" s="5"/>
+      <x:c r="H28" s="5" t="str">
         <x:v>GrantFragmentPack</x:v>
       </x:c>
-      <x:c r="I28"/>
-      <x:c r="J28" t="n">
+      <x:c r="I28" s="5"/>
+      <x:c r="J28" s="5" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K28" t="str">
+      <x:c r="K28" s="5" t="str">
         <x:v>获得餐桌格包(value=候选数)</x:v>
       </x:c>
-      <x:c r="L28"/>
+      <x:c r="L28" s="5"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29" t="str">
+      <x:c r="A29" s="5"/>
+      <x:c r="B29" s="5"/>
+      <x:c r="C29" s="5"/>
+      <x:c r="D29" s="5"/>
+      <x:c r="E29" s="5"/>
+      <x:c r="F29" s="5"/>
+      <x:c r="G29" s="5"/>
+      <x:c r="H29" s="5" t="str">
         <x:v>AddShopPricePct</x:v>
       </x:c>
-      <x:c r="I29"/>
-      <x:c r="J29" t="n">
+      <x:c r="I29" s="5"/>
+      <x:c r="J29" s="5" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K29" t="str">
+      <x:c r="K29" s="5" t="str">
         <x:v>商店价格百分比修正(value=0.25 表示 +25%)</x:v>
       </x:c>
-      <x:c r="L29"/>
+      <x:c r="L29" s="5"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30" t="str">
+      <x:c r="A30" s="5"/>
+      <x:c r="B30" s="5"/>
+      <x:c r="C30" s="5"/>
+      <x:c r="D30" s="5"/>
+      <x:c r="E30" s="5"/>
+      <x:c r="F30" s="5"/>
+      <x:c r="G30" s="5"/>
+      <x:c r="H30" s="5" t="str">
         <x:v>AddChoiceCountPenalty</x:v>
       </x:c>
-      <x:c r="I30"/>
-      <x:c r="J30" t="n">
+      <x:c r="I30" s="5"/>
+      <x:c r="J30" s="5" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K30" t="str">
+      <x:c r="K30" s="5" t="str">
         <x:v>后续奖励候选数惩罚(value=次数,param=数量变化,如 -1)</x:v>
       </x:c>
-      <x:c r="L30"/>
+      <x:c r="L30" s="5"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31" t="str">
+      <x:c r="A31" s="5"/>
+      <x:c r="B31" s="5"/>
+      <x:c r="C31" s="5"/>
+      <x:c r="D31" s="5"/>
+      <x:c r="E31" s="5"/>
+      <x:c r="F31" s="5"/>
+      <x:c r="G31" s="5"/>
+      <x:c r="H31" s="5" t="str">
         <x:v>AddNextFoodTargetOffset</x:v>
       </x:c>
-      <x:c r="I31"/>
-      <x:c r="J31" t="n">
+      <x:c r="I31" s="5"/>
+      <x:c r="J31" s="5" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K31" t="str">
+      <x:c r="K31" s="5" t="str">
         <x:v>下一场经营挑战目标美味值隐藏分偏移(value=偏移)</x:v>
       </x:c>
-      <x:c r="L31"/>
+      <x:c r="L31" s="5"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32" t="str">
+      <x:c r="A32" s="5"/>
+      <x:c r="B32" s="5"/>
+      <x:c r="C32" s="5"/>
+      <x:c r="D32" s="5"/>
+      <x:c r="E32" s="5"/>
+      <x:c r="F32" s="5"/>
+      <x:c r="G32" s="5"/>
+      <x:c r="H32" s="5" t="str">
         <x:v>AddNextMealGold</x:v>
       </x:c>
-      <x:c r="I32"/>
-      <x:c r="J32" t="n">
+      <x:c r="I32" s="5"/>
+      <x:c r="J32" s="5" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K32" t="str">
+      <x:c r="K32" s="5" t="str">
         <x:v>下一场经营挑战奖励额外金币(value=金币)</x:v>
       </x:c>
-      <x:c r="L32"/>
+      <x:c r="L32" s="5"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33" t="str">
+      <x:c r="A33" s="5"/>
+      <x:c r="B33" s="5"/>
+      <x:c r="C33" s="5"/>
+      <x:c r="D33" s="5"/>
+      <x:c r="E33" s="5"/>
+      <x:c r="F33" s="5"/>
+      <x:c r="G33" s="5"/>
+      <x:c r="H33" s="5" t="str">
         <x:v>RemoveActiveItemsForGold</x:v>
       </x:c>
-      <x:c r="I33"/>
-      <x:c r="J33" t="n">
+      <x:c r="I33" s="5"/>
+      <x:c r="J33" s="5" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K33" t="str">
+      <x:c r="K33" s="5" t="str">
         <x:v>失去所有消耗品并按件获得金币(value=每件金币)</x:v>
       </x:c>
-      <x:c r="L33"/>
+      <x:c r="L33" s="5"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34"/>
-      <x:c r="C34"/>
-      <x:c r="D34"/>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
-      <x:c r="G34"/>
-      <x:c r="H34" t="str">
+      <x:c r="A34" s="5"/>
+      <x:c r="B34" s="5"/>
+      <x:c r="C34" s="5"/>
+      <x:c r="D34" s="5"/>
+      <x:c r="E34" s="5"/>
+      <x:c r="F34" s="5"/>
+      <x:c r="G34" s="5"/>
+      <x:c r="H34" s="5" t="str">
         <x:v>IncrementEventCounter</x:v>
       </x:c>
-      <x:c r="I34"/>
-      <x:c r="J34" t="n">
+      <x:c r="I34" s="5"/>
+      <x:c r="J34" s="5" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K34" t="str">
+      <x:c r="K34" s="5" t="str">
         <x:v>增加事件计数并可触发强制事件(value=阈值,param=counterId|eventId)</x:v>
       </x:c>
-      <x:c r="L34"/>
+      <x:c r="L34" s="5"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35" t="str">
+      <x:c r="A35" s="5"/>
+      <x:c r="B35" s="5"/>
+      <x:c r="C35" s="5"/>
+      <x:c r="D35" s="5"/>
+      <x:c r="E35" s="5"/>
+      <x:c r="F35" s="5"/>
+      <x:c r="G35" s="5"/>
+      <x:c r="H35" s="5" t="str">
         <x:v>GainRandomFlavoredDishes</x:v>
       </x:c>
-      <x:c r="I35"/>
-      <x:c r="J35" t="n">
+      <x:c r="I35" s="5"/>
+      <x:c r="J35" s="5" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K35" t="str">
+      <x:c r="K35" s="5" t="str">
         <x:v>获得随机带风味食物(value=数量)</x:v>
       </x:c>
-      <x:c r="L35"/>
+      <x:c r="L35" s="5"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36"/>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36"/>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36" t="str">
+      <x:c r="A36" s="5"/>
+      <x:c r="B36" s="5"/>
+      <x:c r="C36" s="5"/>
+      <x:c r="D36" s="5"/>
+      <x:c r="E36" s="5"/>
+      <x:c r="F36" s="5"/>
+      <x:c r="G36" s="5"/>
+      <x:c r="H36" s="5" t="str">
         <x:v>LoseAllGold</x:v>
       </x:c>
-      <x:c r="I36"/>
-      <x:c r="J36" t="n">
+      <x:c r="I36" s="5"/>
+      <x:c r="J36" s="5" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K36" t="str">
+      <x:c r="K36" s="5" t="str">
         <x:v>金币归零</x:v>
       </x:c>
-      <x:c r="L36"/>
+      <x:c r="L36" s="5"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37" t="str">
+      <x:c r="A37" s="5"/>
+      <x:c r="B37" s="5"/>
+      <x:c r="C37" s="5"/>
+      <x:c r="D37" s="5"/>
+      <x:c r="E37" s="5"/>
+      <x:c r="F37" s="5"/>
+      <x:c r="G37" s="5"/>
+      <x:c r="H37" s="5" t="str">
         <x:v>GainLegendaryItem</x:v>
       </x:c>
-      <x:c r="I37"/>
-      <x:c r="J37" t="n">
+      <x:c r="I37" s="5"/>
+      <x:c r="J37" s="5" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K37" t="str">
+      <x:c r="K37" s="5" t="str">
         <x:v>获得传奇装饰品，缺少传奇时回退高品质被动</x:v>
       </x:c>
-      <x:c r="L37"/>
+      <x:c r="L37" s="5"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38"/>
-      <x:c r="B38"/>
-      <x:c r="C38"/>
-      <x:c r="D38"/>
-      <x:c r="E38"/>
-      <x:c r="F38"/>
-      <x:c r="G38"/>
-      <x:c r="H38" t="str">
+      <x:c r="A38" s="5"/>
+      <x:c r="B38" s="5"/>
+      <x:c r="C38" s="5"/>
+      <x:c r="D38" s="5"/>
+      <x:c r="E38" s="5"/>
+      <x:c r="F38" s="5"/>
+      <x:c r="G38" s="5"/>
+      <x:c r="H38" s="5" t="str">
         <x:v>UiTodo</x:v>
       </x:c>
-      <x:c r="I38"/>
-      <x:c r="J38" t="n">
+      <x:c r="I38" s="5"/>
+      <x:c r="J38" s="5" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K38" t="str">
+      <x:c r="K38" s="5" t="str">
         <x:v>需要后续 UI 选目标的占位效果(param=提示)</x:v>
       </x:c>
-      <x:c r="L38"/>
+      <x:c r="L38" s="5"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39"/>
-      <x:c r="B39"/>
-      <x:c r="C39"/>
-      <x:c r="D39"/>
-      <x:c r="E39"/>
-      <x:c r="F39"/>
-      <x:c r="G39"/>
-      <x:c r="H39" t="str">
+      <x:c r="A39" s="5"/>
+      <x:c r="B39" s="5"/>
+      <x:c r="C39" s="5"/>
+      <x:c r="D39" s="5"/>
+      <x:c r="E39" s="5"/>
+      <x:c r="F39" s="5"/>
+      <x:c r="G39" s="5"/>
+      <x:c r="H39" s="5" t="str">
         <x:v>RemoveRandomRecipeDish</x:v>
       </x:c>
-      <x:c r="I39"/>
-      <x:c r="J39" t="n">
+      <x:c r="I39" s="5"/>
+      <x:c r="J39" s="5" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K39" t="str">
+      <x:c r="K39" s="5" t="str">
         <x:v>随机删除食谱食物(value=数量,param=flavored时只删带风味菜)</x:v>
       </x:c>
-      <x:c r="L39"/>
+      <x:c r="L39" s="5"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40"/>
-      <x:c r="B40"/>
-      <x:c r="C40"/>
-      <x:c r="D40"/>
-      <x:c r="E40"/>
-      <x:c r="F40"/>
-      <x:c r="G40"/>
-      <x:c r="H40" t="str">
+      <x:c r="A40" s="5"/>
+      <x:c r="B40" s="5"/>
+      <x:c r="C40" s="5"/>
+      <x:c r="D40" s="5"/>
+      <x:c r="E40" s="5"/>
+      <x:c r="F40" s="5"/>
+      <x:c r="G40" s="5"/>
+      <x:c r="H40" s="5" t="str">
         <x:v>SelectRemoveRecipeDish</x:v>
       </x:c>
-      <x:c r="I40"/>
-      <x:c r="J40" t="n">
+      <x:c r="I40" s="5"/>
+      <x:c r="J40" s="5" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K40" t="str">
+      <x:c r="K40" s="5" t="str">
         <x:v>交互选择并删除食谱中1 个食物(事件专用)</x:v>
       </x:c>
-      <x:c r="L40"/>
+      <x:c r="L40" s="5"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41"/>
-      <x:c r="B41"/>
-      <x:c r="C41"/>
-      <x:c r="D41"/>
-      <x:c r="E41"/>
-      <x:c r="F41"/>
-      <x:c r="G41"/>
-      <x:c r="H41" t="str">
+      <x:c r="A41" s="5"/>
+      <x:c r="B41" s="5"/>
+      <x:c r="C41" s="5"/>
+      <x:c r="D41" s="5"/>
+      <x:c r="E41" s="5"/>
+      <x:c r="F41" s="5"/>
+      <x:c r="G41" s="5"/>
+      <x:c r="H41" s="5" t="str">
         <x:v>CollectInterest</x:v>
       </x:c>
-      <x:c r="I41"/>
-      <x:c r="J41" t="n">
+      <x:c r="I41" s="5"/>
+      <x:c r="J41" s="5" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K41" t="str">
+      <x:c r="K41" s="5" t="str">
         <x:v>按当前金币及运行时利息参数结算；param=事件ID，读取event.resultText模板</x:v>
       </x:c>
-      <x:c r="L41"/>
+      <x:c r="L41" s="5"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42"/>
-      <x:c r="B42"/>
-      <x:c r="C42"/>
-      <x:c r="D42"/>
-      <x:c r="E42"/>
-      <x:c r="F42"/>
-      <x:c r="G42"/>
-      <x:c r="H42" t="str">
+      <x:c r="A42" s="5"/>
+      <x:c r="B42" s="5"/>
+      <x:c r="C42" s="5"/>
+      <x:c r="D42" s="5"/>
+      <x:c r="E42" s="5"/>
+      <x:c r="F42" s="5"/>
+      <x:c r="G42" s="5"/>
+      <x:c r="H42" s="5" t="str">
         <x:v>AddBusinessGoldPct</x:v>
       </x:c>
-      <x:c r="I42"/>
-      <x:c r="J42" t="n">
+      <x:c r="I42" s="5"/>
+      <x:c r="J42" s="5" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K42" t="str">
+      <x:c r="K42" s="5" t="str">
         <x:v>营业基础金币百分比修正(value=百分比,param=Next/CurrentWeek)</x:v>
       </x:c>
-      <x:c r="L42"/>
+      <x:c r="L42" s="5"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43"/>
-      <x:c r="B43"/>
-      <x:c r="C43"/>
-      <x:c r="D43"/>
-      <x:c r="E43"/>
-      <x:c r="F43"/>
-      <x:c r="G43"/>
-      <x:c r="H43" t="str">
+      <x:c r="A43" s="5"/>
+      <x:c r="B43" s="5"/>
+      <x:c r="C43" s="5"/>
+      <x:c r="D43" s="5"/>
+      <x:c r="E43" s="5"/>
+      <x:c r="F43" s="5"/>
+      <x:c r="G43" s="5"/>
+      <x:c r="H43" s="5" t="str">
         <x:v>AddAllRecipeScoreFlat</x:v>
       </x:c>
-      <x:c r="I43"/>
-      <x:c r="J43" t="n">
+      <x:c r="I43" s="5"/>
+      <x:c r="J43" s="5" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K43" t="str">
+      <x:c r="K43" s="5" t="str">
         <x:v>触发时食谱中已有的全部食物永久分数增加(value=分数)</x:v>
       </x:c>
-      <x:c r="L43"/>
+      <x:c r="L43" s="5"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44"/>
-      <x:c r="B44"/>
-      <x:c r="C44"/>
-      <x:c r="D44"/>
-      <x:c r="E44"/>
-      <x:c r="F44"/>
-      <x:c r="G44"/>
-      <x:c r="H44" t="str">
+      <x:c r="A44" s="5"/>
+      <x:c r="B44" s="5"/>
+      <x:c r="C44" s="5"/>
+      <x:c r="D44" s="5"/>
+      <x:c r="E44" s="5"/>
+      <x:c r="F44" s="5"/>
+      <x:c r="G44" s="5"/>
+      <x:c r="H44" s="5" t="str">
         <x:v>AddBossTargetScorePct</x:v>
       </x:c>
-      <x:c r="I44"/>
-      <x:c r="J44" t="n">
+      <x:c r="I44" s="5"/>
+      <x:c r="J44" s="5" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K44" t="str">
+      <x:c r="K44" s="5" t="str">
         <x:v>后续星级评鉴目标美味值永久百分比修正(value=百分比)</x:v>
       </x:c>
-      <x:c r="L44"/>
+      <x:c r="L44" s="5"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45"/>
-      <x:c r="B45"/>
-      <x:c r="C45"/>
-      <x:c r="D45"/>
-      <x:c r="E45"/>
-      <x:c r="F45"/>
-      <x:c r="G45"/>
-      <x:c r="H45" t="str">
+      <x:c r="A45" s="5"/>
+      <x:c r="B45" s="5"/>
+      <x:c r="C45" s="5"/>
+      <x:c r="D45" s="5"/>
+      <x:c r="E45" s="5"/>
+      <x:c r="F45" s="5"/>
+      <x:c r="G45" s="5"/>
+      <x:c r="H45" s="5" t="str">
         <x:v>AddBossBaseGoldPct</x:v>
       </x:c>
-      <x:c r="I45"/>
-      <x:c r="J45" t="n">
+      <x:c r="I45" s="5"/>
+      <x:c r="J45" s="5" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K45" t="str">
+      <x:c r="K45" s="5" t="str">
         <x:v>后续星级评鉴基础金币永久百分比修正(value=百分比)</x:v>
       </x:c>
-      <x:c r="L45"/>
+      <x:c r="L45" s="5"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46"/>
-      <x:c r="B46"/>
-      <x:c r="C46"/>
-      <x:c r="D46"/>
-      <x:c r="E46"/>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46" t="str">
+      <x:c r="A46" s="5"/>
+      <x:c r="B46" s="5"/>
+      <x:c r="C46" s="5"/>
+      <x:c r="D46" s="5"/>
+      <x:c r="E46" s="5"/>
+      <x:c r="F46" s="5"/>
+      <x:c r="G46" s="5"/>
+      <x:c r="H46" s="5" t="str">
         <x:v>GrantRandomActiveItems</x:v>
       </x:c>
-      <x:c r="I46"/>
-      <x:c r="J46" t="n">
+      <x:c r="I46" s="5"/>
+      <x:c r="J46" s="5" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K46" t="str">
+      <x:c r="K46" s="5" t="str">
         <x:v>随机消耗品(value=数量,param=指定ID列表或Adjust；支持放回)</x:v>
       </x:c>
-      <x:c r="L46"/>
+      <x:c r="L46" s="5"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47"/>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47"/>
-      <x:c r="E47"/>
-      <x:c r="F47"/>
-      <x:c r="G47"/>
-      <x:c r="H47" t="str">
+      <x:c r="A47" s="5"/>
+      <x:c r="B47" s="5"/>
+      <x:c r="C47" s="5"/>
+      <x:c r="D47" s="5"/>
+      <x:c r="E47" s="5"/>
+      <x:c r="F47" s="5"/>
+      <x:c r="G47" s="5"/>
+      <x:c r="H47" s="5" t="str">
         <x:v>GrantRandomPassiveItems</x:v>
       </x:c>
-      <x:c r="I47"/>
-      <x:c r="J47" t="n">
+      <x:c r="I47" s="5"/>
+      <x:c r="J47" s="5" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K47" t="str">
+      <x:c r="K47" s="5" t="str">
         <x:v>随机装饰品(value=数量,param=Positive/Negative)</x:v>
       </x:c>
-      <x:c r="L47"/>
+      <x:c r="L47" s="5"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48"/>
-      <x:c r="B48"/>
-      <x:c r="C48"/>
-      <x:c r="D48"/>
-      <x:c r="E48"/>
-      <x:c r="F48"/>
-      <x:c r="G48"/>
-      <x:c r="H48" t="str">
+      <x:c r="A48" s="5"/>
+      <x:c r="B48" s="5"/>
+      <x:c r="C48" s="5"/>
+      <x:c r="D48" s="5"/>
+      <x:c r="E48" s="5"/>
+      <x:c r="F48" s="5"/>
+      <x:c r="G48" s="5"/>
+      <x:c r="H48" s="5" t="str">
         <x:v>LoseEscalatingGold</x:v>
       </x:c>
-      <x:c r="I48"/>
-      <x:c r="J48" t="n">
+      <x:c r="I48" s="5"/>
+      <x:c r="J48" s="5" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K48" t="str">
+      <x:c r="K48" s="5" t="str">
         <x:v>递增扣除金币(value=首次金额,param=counterId|每次增量；不足扣到0)</x:v>
       </x:c>
-      <x:c r="L48"/>
+      <x:c r="L48" s="5"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49"/>
-      <x:c r="B49" t="str">
+      <x:c r="A49" s="5"/>
+      <x:c r="B49" s="5" t="str">
         <x:v>FoodActionKind</x:v>
       </x:c>
-      <x:c r="C49" t="str">
+      <x:c r="C49" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="D49" t="str">
+      <x:c r="D49" s="5" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="E49"/>
-      <x:c r="F49" t="str">
+      <x:c r="E49" s="5"/>
+      <x:c r="F49" s="5" t="str">
         <x:v>经营挑战类型：区分日常营业、火热营业与星级评鉴</x:v>
       </x:c>
-      <x:c r="G49"/>
-      <x:c r="H49" t="str">
+      <x:c r="G49" s="5"/>
+      <x:c r="H49" s="5" t="str">
         <x:v>Normal</x:v>
       </x:c>
-      <x:c r="I49"/>
-      <x:c r="J49" t="n">
+      <x:c r="I49" s="5"/>
+      <x:c r="J49" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K49" t="str">
+      <x:c r="K49" s="5" t="str">
         <x:v>日常营业行动</x:v>
       </x:c>
-      <x:c r="L49"/>
+      <x:c r="L49" s="5"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50"/>
-      <x:c r="B50"/>
-      <x:c r="C50"/>
-      <x:c r="D50"/>
-      <x:c r="E50"/>
-      <x:c r="F50"/>
-      <x:c r="G50"/>
-      <x:c r="H50" t="str">
+      <x:c r="A50" s="5"/>
+      <x:c r="B50" s="5"/>
+      <x:c r="C50" s="5"/>
+      <x:c r="D50" s="5"/>
+      <x:c r="E50" s="5"/>
+      <x:c r="F50" s="5"/>
+      <x:c r="G50" s="5"/>
+      <x:c r="H50" s="5" t="str">
         <x:v>Super</x:v>
       </x:c>
-      <x:c r="I50"/>
-      <x:c r="J50" t="n">
+      <x:c r="I50" s="5"/>
+      <x:c r="J50" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K50" t="str">
+      <x:c r="K50" s="5" t="str">
         <x:v>火热营业行动</x:v>
       </x:c>
-      <x:c r="L50"/>
+      <x:c r="L50" s="5"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51"/>
-      <x:c r="B51"/>
-      <x:c r="C51"/>
-      <x:c r="D51"/>
-      <x:c r="E51"/>
-      <x:c r="F51"/>
-      <x:c r="G51"/>
-      <x:c r="H51" t="str">
+      <x:c r="A51" s="5"/>
+      <x:c r="B51" s="5"/>
+      <x:c r="C51" s="5"/>
+      <x:c r="D51" s="5"/>
+      <x:c r="E51" s="5"/>
+      <x:c r="F51" s="5"/>
+      <x:c r="G51" s="5"/>
+      <x:c r="H51" s="5" t="str">
         <x:v>Feast</x:v>
       </x:c>
-      <x:c r="I51"/>
-      <x:c r="J51" t="n">
+      <x:c r="I51" s="5"/>
+      <x:c r="J51" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K51" t="str">
+      <x:c r="K51" s="5" t="str">
         <x:v>星级评鉴</x:v>
       </x:c>
-      <x:c r="L51"/>
+      <x:c r="L51" s="5"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="5"/>
+      <x:c r="B52" s="5" t="str">
+        <x:v>ActionRandomCategory</x:v>
+      </x:c>
+      <x:c r="C52" s="5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D52" s="5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="E52" s="5"/>
+      <x:c r="F52" s="5" t="str">
+        <x:v>日常行动随机类别：具体行动从现有 behavior 与 Food.actionKind 推导</x:v>
+      </x:c>
+      <x:c r="G52" s="5"/>
+      <x:c r="H52" s="5" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="I52" s="5"/>
+      <x:c r="J52" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K52" s="5" t="str">
+        <x:v>日常营业</x:v>
+      </x:c>
+      <x:c r="L52" s="5"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="5"/>
+      <x:c r="B53" s="5"/>
+      <x:c r="C53" s="5"/>
+      <x:c r="D53" s="5"/>
+      <x:c r="E53" s="5"/>
+      <x:c r="F53" s="5"/>
+      <x:c r="G53" s="5"/>
+      <x:c r="H53" s="5" t="str">
+        <x:v>Hot</x:v>
+      </x:c>
+      <x:c r="I53" s="5"/>
+      <x:c r="J53" s="5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K53" s="5" t="str">
+        <x:v>火热营业</x:v>
+      </x:c>
+      <x:c r="L53" s="5"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="5"/>
+      <x:c r="B54" s="5"/>
+      <x:c r="C54" s="5"/>
+      <x:c r="D54" s="5"/>
+      <x:c r="E54" s="5"/>
+      <x:c r="F54" s="5"/>
+      <x:c r="G54" s="5"/>
+      <x:c r="H54" s="5" t="str">
+        <x:v>Event</x:v>
+      </x:c>
+      <x:c r="I54" s="5"/>
+      <x:c r="J54" s="5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K54" s="5" t="str">
+        <x:v>事件</x:v>
+      </x:c>
+      <x:c r="L54" s="5"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
